--- a/docs/triton-learning/cards/triton-lesson-06-fused-attention-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-06-fused-attention-technical-qa.xlsx
@@ -36,15 +36,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">单个 head 的 Attention 完整计算是什么？</t>
+          <t xml:space="preserve">在一个 attention head 内，Q、K、V 都是形状为 \[N,D\] 的张量，分别表示 N 个 token 的 query、key 和 value；s 是给定的点积分数缩放系数。暂不考虑分块，如何由它们计算输出 O？说明各阶段的作用和结果形状。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先计算 query–key 分数，再沿 key 轴归一化，最后加权汇总 V。
-• [T#B#输入]：本课 Q、K、V 均为 \[N,D\]；s 是原始 sm_scale，S/P 为 \[N,N\]，O 为 \[N,D\]。
-[E##S=sQK^{\mathsf T},\quad P=\operatorname{softmax}_{\mathrm{key}}(S),\quad O=PV]
-[T#B,!c47f17#边界]：causal 只允许 j≤i；Q/K/V 的线性投影和后续多头输出投影不属于这个算子。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先让每个 query 与所有 key 计算匹配分数，再把该行分数归一化为权重，最后用这些权重汇总 value。
+• [T#B#匹配分数]：S=sQKᵀ 的形状为 \[N,N\]。S\[i,j\] 是 query i 与 key j 的缩放点积；它此时还没有取指数，也不是概率。
+• [T#B#归一化]：沿 S 的每一行，也就是 key 轴做 softmax，得到同形状的 P。P\[i,j\] 是 query i 分配给 value j 的权重；每个有效行的权重和为 1。
+• [T#B#输出]：O=PV 的形状为 \[N,D\]。O\[i,:\] 是第 i 个 query 对所有有效 value 向量的加权和，仍保留 D 个特征。
+[E##S=sQK^{\mathsf T},\qquad P=\operatorname{softmax}_{\mathrm{key}}(S),\qquad O=PV]
+[T#B,!c47f17#边界]：causal 模式只允许 key 索引 j≤query 索引 i，包含自身；无效位置不参与归一化。这里的 Q/K/V 已由调用方生成，前面的线性投影和后面的多头输出投影都不属于此算子。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -61,14 +63,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FlashAttention 避免了哪项开销？</t>
+          <t xml:space="preserve">普通 Attention 会把 N 个 query 对 N 个 key 的分数矩阵 S，以及 softmax 概率矩阵 P，写入全局显存。FlashAttention 改为按块计算时，主要避免了什么开销？QKᵀ 和 PV 的计算量是否也因此消失？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：避免将完整的 score 和概率矩阵写入、再读出全局显存。
-• [T#B#仍需计算]：QKᵀ 与 PV 的主要矩阵乘仍要进行；分块在线归一化不消除序列长度的平方级计算。
-[T#B,!c47f17#边界]：显存流量下降不等于固定倍数的加速，速度仍取决于硬件、形状和实现。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：主要省去完整 N×N 中间矩阵的物化及其显存读写；QKᵀ 和 PV 的主要计算仍然需要完成。
+• [T#B#普通路径]：先写出完整 S，再读取它求 softmax 并写出 P，最后读取 P 与 V 相乘，会产生大量中间数据的存储和搬运。
+• [T#B#分块路径]：固定一个 Q 块，逐块读取 K/V；分数和指数权重只作为当前块的临时量，旧块的影响由少量逐行统计量及输出累加器保留。
+• [T#B#计算边界]：仍需对相关 query–key 对计算分数，并把权重作用到 V。对完整非因果注意力，主要矩阵乘工作量仍随 N²D 增长。
+[T#B,!c47f17#边界]：减少显存流量是优化机制，不是固定倍数的加速承诺。实际耗时还与 GPU、输入形状、分块及实现有关。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -85,15 +89,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">前向 grid 怎样分配输出块？</t>
+          <t xml:space="preserve">在所学 FP16 Attention 前向中，输入 Q/K/V 的形状是 \[B,H,N,D\]：B 为 batch 数、H 为 head 数、N 为 token 数、D 为每个 head 的特征维。BLOCK_M 是一个 Q tile 的行数。grid=(ceil(N/BLOCK_M),B×H,1) 怎样把计算和最终输出分给各 program？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：一个 program 固定一个 batch/head 的 Q tile，并独占对应 O 行块和 M 行统计量。
-• [T#B#grid]：(ceil(N/BLOCK_M), B×H, 1)：第 0 轴选 Q tile，第 1 轴选 batch/head；第三轴仅一个位置，可省略。
-• [T#B#扫描]：program 内扫描所需 K/V 块，扫描轮数不是 program 数。
-[T#B,!c47f17#边界]：这些轴的含义来自所学 kernel 的 program_id 用法，不是 Triton 对每个轴预设的业务含义。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：每个 program 固定一个 batch/head 和一个 Q 行块，扫描这个行块需要的 K/V，最终独占写回对应的 O 行块及 M 行统计量。
+• [T#B#第0轴]：program_id(0) 选择 Q tile。编号为 p 的 tile 对应 head 内从 p×BLOCK_M 开始的 query 行。
+• [T#B#第1轴]：program_id(1) 选择合并后的 batch/head 编号 g；可由 b=g//H、h=g%H 还原到具体输入切片。
+• [T#B#内部循环]：K/V 的分块扫描在同一个 program 内完成。扫描多少轮与启动多少个 program 是不同概念；这个前向不是每个 Q×K 块都启动一个独立 program。
+• [T#B#第2轴]：尾部 1 表示第三轴只有一个位置。本实现没有使用该轴，把 grid 写成前两维即可表达相同分工。
+[T#B,!c47f17#边界]：grid 轴的业务含义来自 kernel 如何使用 program_id。它们不是 Triton 预先规定的 query、batch、head 轴。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -110,15 +116,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FP16 的 \[BHN,D\] 视图怎样定位 token 行？</t>
+          <t xml:space="preserve">连续 FP16 Q/K/V 原本形状为 \[B,H,N,D\]，B/H 分别为 batch/head 数，N 为 token 数，D 为特征维。现在 descriptor 将 batch、head、token 合并成 \[BHN,D\] 的二维视图。已知 batch=b、head=h、head 内 token=t，这个 token 在 descriptor 中的全局行号怎样计算？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：加上当前 batch/head 的整段序列基址。
-[E##g=bH+h,\quad r=gN+t]
-• [T#B#历史误区]：head 内 token 2、3 不能直接当全局行；g=5、N=8 时对应全局行 42、43。
-[T#B,!c47f17#边界]：限定本课 FP16 的 \[BHN,D\] 普通视图；Q 起点和 K/V 扫描起点都加同一 head 基址。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先求当前 batch/head 的序列起点，再加上该 head 内的 token 索引。
+[E##g=bH+h,\qquad r=gN+t]
+• [T#B#各量含义]：g 是合并后的 batch/head 编号，每个 g 占连续 N 行；因此 gN 是该 head 的首行，t 才是它内部的局部偏移。特征坐标 d 不参与这一步行号计算。
+• [T#B#例子]：若 g=5、N=8，head 内 token 2、3 应读 descriptor 全局行 42、43。只写行号 2、3 会访问整个视图开头的 head。
+• [T#B#用到哪里]：Q tile 起点和 K/V 的每轮扫描起点都需要加当前 head 基址。判断 causal 的先后关系时，也要保证两个 token 坐标使用同一坐标系。
+[T#B,!c47f17#边界]：这是 FP16 的普通 \[BHN,D\] 视图；FP8 V 的重排 descriptor 使用另一组轴，不能直接套用这套行号公式。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -135,15 +143,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么 acc 的形状是 \[BLOCK_M,D\]？</t>
+          <t xml:space="preserve">分块 Attention 前向中，一个 Q tile 有 B_M 个 query；本轮 K/V tile 有 B_N 个 key/value；每个 value 有 D 个特征。指数权重块的形状是 \[B_M,B_N\]。累加加权 V 的 acc 应是什么形状，为什么不能因 B_M 恰好等于 D 就把它理解成 \[B_M,B_M\]？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：PV 沿 key 轴求和，保留 query 轴与 value 特征轴。
-[E##P_{\rm tile}:B_M\times B_N,\quad V_{\rm tile}:B_N\times D,\quad acc:B_M\times D]
-• [T#B#统计量]：m、l 每个 query 一个值，形状 \[BLOCK_M\]；重标定 acc 时沿特征轴广播 alpha\[:,None\]。
-[T#B,!c47f17#边界]：即使数值上 BLOCK_M=D，也不能把 acc 的第二轴解释成另一个 query 轴。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：acc 的形状是 \[B_M,D\]：每个 query 保留一个 D 维加权 value 向量。
+[E##\underbrace{p}_{B_M\times B_N}\ \underbrace{V}_{B_N\times D}\ \longrightarrow\ \underbrace{acc}_{B_M\times D}]
+• [T#B#归约轴]：乘加时对本轮的 key/value 索引求和，B_N 这一轴被归约；保留下来的是 query 轴 B_M 和 value 特征轴 D。下一轮 K/V 继续加到同一个 acc。
+• [T#B#逐行统计]：运行最大值 m、指数和 l、重标定系数 alpha 都是一 query 一个值，所以形状为 \[B_M\]。给 acc 重标定时用 alpha\[:,None\] 沿 D 轴广播。
+[T#B,!c47f17#边界]：B_M=64、D=64 只是数值偶合，不能改变轴的含义。换成 B_M=32、D=64 时，acc 仍然是 \[32,64\]。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -160,16 +169,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">新 key 块如何并入在线 softmax 状态？</t>
+          <t xml:space="preserve">固定一个 query，Attention 前向已经扫描过若干 K/V 块，并保存运行最大值 m、指数和 l、加权 V 分子 acc。新 key 块 J 的分数 x_j 已换到 exp2 的输入域，但尚未取指数。怎样把这个新块并入旧状态，最终得到该 query 的输出？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先统一到新的行最大值，再同时合并分母 l 与加权 value 分子 acc。
-• [T#B#定义]：固定一个 query 行；x 是换底后的 score，新块为 J；旧状态为 m、l、acc，Q 在扫描中保持不变。
-[E##m'=\max(m,\max_{j\in J}x_j),\quad \alpha=2^{m-m'},\quad p_j=2^{x_j-m'}]
-[E##l'=\alpha l+\sum_{j\in J}p_j,\quad acc'=\alpha acc+\sum_{j\in J}p_jV_j,\quad O=acc/l]
-[T#B,!c47f17#边界]：旧 acc 携带此前 V 的贡献；只保留 m、l 不够。最终是分子除分母。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先选择旧块与新块共同使用的最大值基准，再同步缩放旧分母和旧分子，加入新块贡献。
+• [T#B#旧状态含义]：旧 l 是此前各 key 的 2^(x_j−m) 之和；旧 acc 是这些权重乘 V_j 后的向量和。acc 保存着旧 value 对输出的贡献，不能只留下 m 和 l。
+[E##m'=\max\bigl(m,\max_{j\in J}x_j\bigr),\qquad \alpha=2^{m-m'},\qquad p_j=2^{x_j-m'}]
+[E##l'=\alpha l+\sum_{j\in J}p_j,\qquad acc'=\alpha acc+\sum_{j\in J}p_jV_j]
+• [T#B#为何共同缩放]：旧权重原先减的是 m，现在必须改成减 m′，每一项都恰好多乘 2^(m−m′)。分母和加权分子使用同一批权重，所以必须一起缩放；若最大值不变，alpha=1。
+• [T#B#最终输出]：扫描完所有有效 K/V 后，O=acc/l，其中 acc 是 D 维分子，l 是标量分母。对一个 Q tile 同时做这些操作时，每一行独立维护状态，Q tile 在整个扫描中保持不变。
+[T#B,!c47f17#边界]：p_j 在这里是当前最大值基准下的未归一化指数权重；它不是已经除以整行分母的概率 P_j。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -186,15 +197,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">m=−∞ 时，l 初始为 1 为什么不污染首块？</t>
+          <t xml:space="preserve">所学 Attention 前向将每个 query 的在线状态初始化为 m=−∞、l=1、acc=0。其中 m 是 exp2 输入域分数的运行最大值。假设首块至少有一个有效 key，且所有有效 score 都有限（无效位置可被 mask 为 −∞），为什么初始 l=1 不会使 softmax 分母多出 1？改成 l=0 是否也可行？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：首个有效有限块使新最大值有限，重标定系数为 0，初始 l 被消去。
-[E##\alpha=2^{-\infty-m_{\rm new}}=0,\quad l_{\rm new}=\alpha l_0+\sum_j2^{x_j-m_{\rm new}}]
-• [T#B#等价条件]：此时任意有限 l₀（包括 0、1）都得到相同首块结果；m 若错误地初始化为 0，不能沿用此论证。
-[T#B,!c47f17#边界]：l=1 不能修复 inf−inf 或全无效行的 NaN；源码不足以证明作者选择 1 的动机。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：首块使新最大值变为有限数，因此重标定系数为 0，初始 l 的有限值会被消去；在这些条件下，l 初始为 0 或 1 都可行。
+• [T#B#符号]：令 x_j 表示尚未取指数、已换底为 exp2 标度的有效 key 分数，m_new 是加入首块后的有限最大值；l₀ 是初始的有限分母状态。
+[E##\alpha=2^{-\infty-m_{new}}=0,\qquad l_{new}=\alpha l_0+\sum_j2^{x_j-m_{new}}]
+• [T#B#为什么选m很关键]：这里能消去初值，依赖于 m 的初始值是 −∞。如果误把 m 初始化为 0，而首块所有分数都小于 0，新最大值可能仍是 0，alpha=1，初始 l=1 就会残留。
+• [T#B#异常值边界]：l=1 并不能修复 inf−inf 产生的 NaN；首块全无效或包含异常无穷值时，必须另行定义和处理数值语义。NaN 也不会因为乘 0 自动消失。
+[T#B,!c47f17#边界]：代码行为能解释这种初始化在合法输入下成立，但没有足够证据据此断言作者选择 1 是为了防止某种异常。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -211,15 +224,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">causal 前向怎样划分 key 区域？</t>
+          <t xml:space="preserve">在 causal Attention 前向中，一个 program 负责 head 内 query 区间 \[a,b)。causal 规则是 query i 只能读取 key j≤i。为了减少逐元素 mask，这个 program 应怎样划分要扫描的 key 区域？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：对 Q tile \[a,b)，过去全读、对角加 mask、未来跳过。
-• [T#B#三个区间]：key \[0,a) 对本 Q tile 全有效；\[a,b) 检查 j≤i；\[b,N) 不参与。
-• [T#B#状态]：两段有效扫描接续同一 m/l/acc；第一个 Q tile 的过去区为空。
-[T#B,!c47f17#边界]：上述按 token 范围表达；块的步长和整除条件必须保证实际循环符合这个划分。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：把 key 分成过去区 \[0,a)、对角区 \[a,b) 和未来区 \[b,N)：过去区全有效，对角区逐元素检查，未来区跳过。
+• [T#B#过去区]：对任意 i∈\[a,b)，若 j&lt;a，则 j≤i 恒成立，所以这部分 K/V 块可以直接参与计算。
+• [T#B#对角区]：query 与 key 都在 \[a,b) 内时，有些 key 仍在当前 query 之后，必须按 j≤i 加 mask；当前位置自身也有效。
+• [T#B#未来区]：若 j≥b，则它对整个 Q tile 都在未来，没有有效贡献，可以不扫描。
+• [T#B#状态接续]：过去区和对角区属于同一批 query，必须接续同一个 m/l/acc。第一个 Q tile 的 a=0，过去区为空，实际处理直接从对角区开始。
+[T#B,!c47f17#边界]：这里描述逻辑 token 区间。实际 tile 步长、尾块和整除条件仍需保证循环没有跨过应访问的范围。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -236,16 +251,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么 M=m+log₂(l) 能恢复概率？</t>
+          <t xml:space="preserve">Attention 前向采用 exp2，令 x_j=S_j/ln2，其中 S_j 是已乘原始 scale 的点积分数。它为一行有效 key 保存 m=max(x_j)、l=Σ2^(x_j−m)，并只把 M=m+log₂(l) 留给反向。为什么反向用 2^(x_j−M) 就能恢复概率，且没有丢掉减最大值的稳定化效果？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：M 是整行未减最大值的分母的 log₂；减 M 已包含稳定化和归一化。
-• [T#B#定义]：x=S/ln2；m 是有效 x 的行最大值，l 是减 m 后指数权重之和。
-[E##M=m+\log_2\sum_j2^{x_j-m}=\log_2\sum_j2^{x_j},\quad P_j=2^{x_j-M}]
-• [T#B#稳定性]：对有限有效 score，M≥m≥xⱼ，因此指数不大于 0；减最大值的效果没有消失。
-[T#B,!c47f17#边界]：要求每行至少有一个有限有效项；全屏蔽行、非有限 score 需另行处理，浮点仍可能舍入或下溢。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：M 是整行原始指数和的 log₂；减去 M 同时完成了减最大值和除以归一化分母。
+[E##M=m+\log_2l=\log_2\sum_j2^{x_j}]
+[E##P_j=2^{x_j-M}=\frac{2^{x_j-m}}{l}]
+• [T#B#加回m的作用]：l 是减最大值后得到的指数和，比原始指数和少了因子 2^m。只保存 log₂(l) 会遗漏这个因子；加上 m 才恢复完整分母的对数。
+• [T#B#稳定性]：对一行有限有效 score，最大值对应的指数项为 1，所以 l≥1，进而 M≥m≥x_j。恢复有效概率时指数不大于 0，不会出现指数上溢。
+[T#B,!c47f17#边界]：这个结论限定在有效位置以及前后向使用一致分数的数学运算；全屏蔽行、非有限输入需要单独处理，浮点也仍可能舍入或下溢。M 是 log-sum-exp，不能再把它误认成行最大值 m。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -262,16 +278,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">本课 FP16 前向怎样安排精度？</t>
+          <t xml:space="preserve">在所学 FP16 Attention 前向实现中，Q/K/V 以 FP16 存储，输出 O 也需要返回 FP16。沿 QKᵀ、softmax 在线统计、pV 到 O/M 写回这条路径，各阶段使用什么精度，关键转换发生在哪里？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：矩阵乘使用 FP16 操作数、FP32 累加；归一化与在线状态保留 FP32。
-• [T#B#QKᵀ]：Q/K 为 FP16，score、缩放、指数及 m/l 为 FP32。
-• [T#B#pV]：先用 FP32 p 求分母，再把 p 转 FP16 与 FP16 V 相乘，累加到 FP32 acc。
-• [T#B#写回]：O 转回 FP16，保存的 M 保持 FP32。
-[T#B,!c47f17#边界]：pV 前也发生降精度；并非只有 O 写回时才转换。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：矩阵乘用低精度操作数配合 FP32 累加，归一化与在线状态保留 FP32；中途 pV 前和最终 O 写回前都会发生降精度转换。
+• [T#B#QKᵀ与score]：Q 和 K 是 FP16 操作数，点积累加结果为 FP32。后续缩放、最大值、减最大值和指数权重计算使用 FP32，保护归约和指数相关的数值计算。
+• [T#B#在线状态]：每个 query 的最大值 m、指数和 l，以及 D 维输出分子 acc 都保留 FP32，使跨多个 K/V 块的合并不必每轮舍入到 FP16。
+• [T#B#pV之前]：p 表示当前块的未归一化指数权重。先用 FP32 p 求分母增量，再把 p 转为 FP16，与 FP16 V 相乘；乘积继续累计到 FP32 acc。
+• [T#B#输出]：最后 acc/l 得到归一化输出，O 写回时转成 FP16；供反向重建概率的 M=m+log₂l 仍以 FP32 保存。
+[T#B,!c47f17#边界]：这是该实现的精度安排。调用者看到的输入或输出 dtype，不能代表每一步内部运算精度；也不能概括成“只有最终 O 才转换精度”。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -288,14 +305,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么 p 的分母归约放在转 FP16 之前？</t>
+          <t xml:space="preserve">Attention 前向中，p 是 FP32 的未归一化指数权重块，l 要累加每行的 sum(p)；另一路会把 p 转成 FP16 后与 FP16 V 做矩阵乘。如果把 sum(p) 移到 p 转 FP16 之后，即使仍用 FP32 累加，能保证分母结果不变吗？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先转 FP16 会丢失权重信息，之后再以 FP32 累加也无法恢复。
-• [T#B#所学路径]：用 FP32 指数权重计算 l 的增量；仅为 pV 的矩阵乘把权重转换为 FP16。
-[T#B,!c47f17#边界]：两种求和顺序不保证得到相同数值；FP32 累加只更准确地处理送入它的值。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能保证。FP16 转换已经改变了参与求和的权重，FP32 累加只能更准确地累加这些舍入后的值。
+• [T#B#原顺序]：先对尚未降精度的 FP32 权重求行和，用于更新 l；然后仅为 pV 的矩阵乘把 p 转成 FP16。分母因此保留了转换前的权重信息。
+• [T#B#交换后]：若先转换，传给求和的是 round_fp16(p)，而不是原始 p。即使累加器是 FP32，也无法知道每个元素在转换中丢失了多少低位。
+• [T#B#误差位置]：高精度累加主要减少累加过程引入的误差，不能撤销累加开始前已经发生的输入量化误差。这就是要分别考虑操作数和累加器精度的原因。
+[T#B,!c47f17#边界]：并非每组输入都会产生可见差异，例如恰好能被 FP16 精确表示的权重可能一致；但两个顺序不是普遍数值等价的改写。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -312,15 +331,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">新算子的精度应按什么逻辑选择？</t>
+          <t xml:space="preserve">阅读或设计一个新的深度学习算子时，输入和输出可能使用 FP16，但内部还有矩阵乘、长归约或指数运算。应怎样决定各阶段的精度，而不是凭输入 dtype 猜测全部内部计算类型？</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：在满足数值误差和稳定性要求的前提下降低存储与计算成本。
-• [T#B#步骤]：先看输入范围与容差，再找归约、指数等误差敏感环节，分别决定操作数、累加器与输出类型。
-• [T#B#验证]：明确每次转换位置，用参考结果检验误差，再测量性能收益。
-[T#B,!c47f17#边界]：没有统一的“内部默认全 FP32”配方；输出 dtype 也不能揭示全部内部精度。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先确定允许的数值误差和输入范围，再把精度用在误差容易累积或放大的环节，最后用实验核对数值与成本。
+• [T#B#数值要求]：了解输入可能的大小、动态范围以及输出可接受的误差。有限表示范围可能造成溢出或下溢；有限有效位数可能使舍入误差累积。
+• [T#B#分开选择]：分别判断存储 dtype、实际操作数 dtype、累加器 dtype 和输出 dtype。它们可以不同，例如低精度矩阵乘操作数与高精度累加器配合。
+• [T#B#转换位置]：长归约、指数和归一化通常值得单独检查。明确在哪里升精度、在哪里允许降精度；高精度累加无法弥补早先已经丢失的输入信息。
+• [T#B#验证]：先对照可信参考验证正常与边界输入的误差，再测实际速度和存储收益。只有同时满足所需准确性与成本目标，精度配置才有依据。
+[T#B,!c47f17#边界]：通用的是这套判断方法，不是一套所有算子都适用的 dtype 配方。单凭“输出为 FP16”或“文档没有特别说明”，都不能推断内部始终是 FP16 或 FP32。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -337,15 +358,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">所学前后向怎样跨函数和 kernel 传状态？</t>
+          <t xml:space="preserve">阅读所学 Attention 源码时，会看到前向 kernel 内多次调用 _attn_fwd_inner，也会看到反向先启动 preprocess、再启动主 backward。它们分别怎样传递计算状态？为什么不能把每个 @triton.jit 函数调用都当成独立的 kernel launch？</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：前向 inner 接续局部在线状态；反向两次 Triton launch 通过全局 Delta 缓冲区衔接。
-• [T#B#前向]：inner 是 kernel 内 JIT 辅助函数；外层必须按返回顺序接收更新后的在线状态，供下一个区间使用。
-• [T#B#反向]：preprocess 从 O、dO 写 Delta；主反向读取 Q/K/V、M、dO、Delta 并输出梯度。
-[T#B,!c47f17#边界]：wrapper 还会预缩放 K；两个 Triton launch 不代表反向只有两项 GPU 操作。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：前向 inner 调用在同一个 kernel/program 内接续局部在线状态；反向的两个独立 Triton launch 则通过全局 Delta 缓冲区传递数据。
+• [T#B#前向helper]：_attn_fwd_inner 是 JIT 辅助函数。它更新当前 Q tile 的 m、l、acc，并返回新状态；外层必须按返回顺序重新绑定变量，后续区域才能继续之前的累加。
+• [T#B#前向出错方式]：只调用 helper 却不接收返回值，不能指望 helper 内的重新赋值自动更新外层局部变量。causal 的过去区和对角区就可能失去状态接续。
+• [T#B#反向launch]：_attn_bwd_preprocess 用 O 和 dO 计算 Delta，并写入全局缓冲区；随后主反向读取它，以及 Q、预缩放 K、V、M、dO，生成输入梯度。
+[T#B,!c47f17#边界]：反向 wrapper 还包含 K 的预缩放等操作。因此“两次 Triton kernel 启动”只是在描述这两个显式 launch，不代表整个反向恰好只有两项 GPU 操作。</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -362,17 +384,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 的反向链怎样闭合？</t>
+          <t xml:space="preserve">对一个 head，前向为 S=sQKᵀ、P=softmax_key(S)、O=PV；s 是固定缩放系数，Q/K/V 为 \[N,D\]。损失传来同形状的上游梯度 dO 后，如何依次算出 dP、分数梯度以及 dQ/dK/dV？</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先从 O=PV 回传到 P/V，再通过逐行 softmax 回传到分数，最后回传到 Q/K。
-• [T#B#定义]：S=sQKᵀ，G=∂L/∂S；s 固定，dO 是上游梯度。
-[E##dP=dOV^{\mathsf T},\quad dV=P^{\mathsf T}dO]
-[E##\Delta_i=\sum_jP_{ij}dP_{ij},\quad G_{ij}=P_{ij}(dP_{ij}-\Delta_i)]
-[E##dQ=sGK,\quad dK=sG^{\mathsf T}Q]
-[T#B,!c47f17#边界]：causal 无效位置的 P/G 置零；实现可按 tile 重建 P，无需物化整张矩阵。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：沿前向的相反方向：先从 O=PV 回传到 P/V，再通过每行 softmax 回传到 S，最后通过缩放点积回传到 Q/K。
+• [T#B#记号]：dP 表示损失对概率 P 的梯度；令 G=∂L/∂S，避免把“对自然分数 S 的梯度”与某种源码临时变量混淆。S、P、dP、G 都是 \[N,N\]。
+[E##dP=dOV^{\mathsf T},\qquad dV=P^{\mathsf T}dO]
+[E##\Delta_i=\sum_jP_{ij}dP_{ij},\qquad G_{ij}=P_{ij}(dP_{ij}-\Delta_i)]
+[E##dQ=sGK,\qquad dK=sG^{\mathsf T}Q]
+• [T#B#形状与分块]：dQ/dK/dV 都回到 \[N,D\]。实现可以在需要时按块用 Q/K 和保存的 M 重建 P，再累计这些公式对应的梯度，无需保存完整 N×N 概率。
+[T#B,!c47f17#边界]：causal 模式中，无效 query–key 位置的 P 和 G 均不贡献梯度。这里求的是对 Q/K/V 的梯度，假设 s 固定。</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -389,15 +412,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">M、Delta 应沿概率块的哪个轴广播？</t>
+          <t xml:space="preserve">Attention 反向重建一个概率 tile 时，M 和 Delta 都是“每个 query 一个值”的统计量。如果概率 tile 有时按 \[Bq,Bk\]（query×key）存放，有时按 \[Bk,Bq\]（key×query）存放，这两个向量应怎样广播才能对应到正确 query？</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：始终保持一个 query 对应一个统计量，沿 key 轴广播。
-• [T#B#query × key]：形状 \[Bq,Bk\] 时，用 M\[:,None\] 和 Delta\[:,None\]。
-• [T#B#key × query]：形状 \[Bk,Bq\] 时，用 M\[None,:\] 和 Delta\[None,:\]。
-[T#B,!c47f17#边界]：按轴的语义决定，不能看到同名变量就机械复制另一条路径的写法。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先找出概率 tile 的 query 轴，让每个统计量保持与对应 query 的绑定，再沿 key 轴复制。
+• [T#B#query在行]：对于 \[Bq,Bk\]，M 与 Delta 的形状都是 \[Bq\]。用 M\[:,None\]、Delta\[:,None\] 得到 \[Bq,1\]，向同一 query 的各个 key 列广播。
+• [T#B#query在列]：对于 \[Bk,Bq\]，query 是第二轴。用 M\[None,:\]、Delta\[None,:\] 得到 \[1,Bq\]，向各个 key 行广播。
+• [T#B#为什么会不同]：所学 dQ 路径固定 Q 并扫描 K/V，使用 query×key 布局；dK/dV 路径固定 K/V 扫描 Q，使用转置的 key×query 布局。
+[T#B,!c47f17#边界]：不能按变量名照抄另一路的 \[:,None\] 或 \[None,:\]。M 用来恢复概率，Delta 用来计算 softmax 梯度，但它们都必须跟随 query 轴。</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -414,15 +438,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">何时可以不用 atomic 写回 dK/dV？</t>
+          <t xml:space="preserve">分块计算 Attention 的 dK/dV 时，同一个 key 会接收多个 query 的梯度贡献。什么样的 program 分工可以在写回这些梯度时不用 atomic？如果把同一输出块的贡献拆给两个 program，为什么普通 store 不够？</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：一个 program 汇总某个输出 tile 的全部有效贡献，并独占写回时。
-• [T#B#归约]：固定 K/V tile，扫描所有参与贡献的 query 块，在 program 内累加。
-• [T#B#若拆分]：多个 program 只算部分和时，要用 atomic 或临时缓冲区加后续归约；普通 store 不会求和。
-[T#B,!c47f17#边界]：即便多个 store 按顺序执行，后写仍会覆盖前写。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：让一个 program 算齐某个 dK/dV 输出块的全部贡献，并让它成为该块唯一的写入者，就无需跨 program 的 atomic 累加。
+• [T#B#完整归约]：固定一个 K/V tile 后，负责它的 program 扫描所有有效 query 块，在自己的累加器中把各块贡献求和。扫描结束后只写回一次完整结果。
+• [T#B#独占输出]：不同 program 可以并行计算不同 K/V 输出块，因为它们的写入位置不重叠；许多 query 参与同一输出，并不必然意味着许多 program 写同一地址。
+• [T#B#拆分后的要求]：若两个 program 分别得到 A 和 B，最终结果需要 A+B。普通 store 只覆盖目标值，即使强制顺序也不会自动求和；可用 atomic，或分别写临时缓冲区后再归约。
+[T#B,!c47f17#边界]：无需 atomic 的前提是“单个 program 完成完整归约且独占输出”。不能把它推广为所有 Attention 反向实现都不需要同步或归约。</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,15 +464,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">causal 反向为什么沿两个方向扫描？</t>
+          <t xml:space="preserve">causal Attention 规定 query i 只能使用 key j≤i。反向计算时，固定一个 query 来求 dQ，与固定一个 key 来求 dK/dV，分别要汇总哪一侧 token 的贡献？为什么扫描方向看起来相反？</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：同一个约束 j≤i，从固定 query 和固定 key 两侧看，得到不同归约范围。
-• [T#B#固定 query i]：dQᵢ 汇总 key j≤i，沿 key 轴扫描。
-• [T#B#固定 key j]：dKⱼ、dVⱼ 汇总 query i≥j，沿 query 轴扫描。
-[T#B,!c47f17#边界]：包含当前位置；对角 tile 仍需逐元素 mask。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它们来自同一个因果约束，只是固定的索引不同：固定 i 时取 j≤i，固定 j 时取 i≥j。
+• [T#B#dQ的归约]：求 query i 的 dQ，需要汇总它看得到的 key，所以扫描该位置及此前的 key：0≤j≤i。未来 key 从未参与其前向输出，没有对应贡献。
+• [T#B#dK/dV的归约]：求 key/value j 的梯度，需要找到所有用过它的 query；这些 query 位于 j 及之后，即 j≤i&lt;N。更早的 query 看不到这个未来 key。
+• [T#B#分块时]：固定 query tile 通常扫描过去 key 区和对角区；固定 key tile 则扫描对角 query 区和后续区。对角块内部还要按逐元素 i/j 关系加 mask。
+[T#B,!c47f17#边界]：两种范围都包含当前位置自身。不要把前向的“query 看过去 key”机械改写成“key 的梯度也只看过去 query”。</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -464,15 +490,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么 dQ 末尾乘 ln2，而 dK 乘 s？</t>
+          <t xml:space="preserve">所学 Attention 反向先把 K 预缩放为 K̃=(s/ln2)K。令 G=P⊙(dP−Delta) 表示损失对自然分数 S=sQKᵀ 的梯度。为什么 dQ 路径用 K̃ 累加后要乘 ln2，而 dK 路径用原始 Q 累加后要乘 s？</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：两条路径输入中的预缩放不同，末尾系数用于恢复同一数学梯度。
-• [T#B#输入]：wrapper 给 K̃=(s/ln2)K；G=P⊙(dP−Delta) 表示对自然分数 S=sQKᵀ 的梯度。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：末尾系数是在补回各路径尚缺或多带的缩放；两条路径输入中的 scale 并不相同。
+• [T#B#dQ路径]：数学目标是 dQ=sGK。使用预缩放 K̃ 后，临时结果为 GK̃=(s/ln2)GK，已含 s，却多了 1/ln2，因此最后乘 ln2。
+• [T#B#dK路径]：数学目标是 dK=sGᵀQ。该路径使用原始 Q 得到 GᵀQ，尚未包含 s，所以在写回前乘 s。
 [E##(G\widetilde K)\ln2=sGK=dQ,\qquad s(G^{\mathsf T}Q)=dK]
-[T#B,!c47f17#边界]：漏乘 ln2 得到 dQ 的 1/ln2 倍；dV=PᵀdO 不需要这两项缩放。</t>
+• [T#B#常见遗漏]：如果漏掉 dQ 的末尾 ln2，结果会是正确 dQ 的 1/ln2 倍。dV=PᵀdO 则没有上述点积分数缩放，不需要这两项系数。
+[T#B,!c47f17#边界]：必须追踪这个版本 wrapper 与 kernel 实际使用的张量。这里的 G 是对自然分数 S 的梯度；若另一实现选择不同表示域或预缩放位置，不能照搬末尾系数。</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -489,16 +517,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">descriptor 怎样确定一次 load 读取的块？</t>
+          <t xml:space="preserve">使用 Triton TensorDescriptor 按块读取张量时，base、shape、strides、block_shape 和 load(offsets) 分别决定什么？例如 B/H/N/D 分别表示 batch 数、head 数、token 数和特征维，Q 被展平成 \[BHN,D\]，每次取 BLOCK_M 个 query。此时 block_shape=\[BLOCK_M,D\]，load(\[r0,0\]) 会读取哪个块？</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：整体存储布局、块大小与本次起点共同确定读取范围。
-• [T#B#整体视图]：base 定位已有存储；shape 给出整个访问视图的各维大小；strides 给出各维前进一步对应的元素偏移。
-• [T#B#块大小]：block_shape 指定每次返回的 tile 形状。
-• [T#B#块起点]：load 的 offsets 指定本次块起点；改变起点会移动读取位置，不会改变返回形状。
-[T#B,!c47f17#边界]：offsets 是本次 load 的参数；创建 descriptor 只是描述存储，不会提前读取整张量。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：descriptor 给出全局存储视图与每次访问块的形状；load 的 offsets 再指定这一次从视图中的哪个坐标开始。
+• [T#B#base与shape]：base 是已有张量存储的首地址；shape=\[BHN,D\] 声明一个有 BHN 行、D 列的访问视图。创建 descriptor 只是建立访问描述，不会提前读取整个张量。
+• [T#B#strides]：strides 表示某一维索引增加 1 时跨过多少个元素，而不是字节。连续二维视图通常为 \[D,1\]；换算实际字节偏移还要乘元素字节数。
+• [T#B#block_shape]：\[BLOCK_M,D\] 指定每次 load 返回 BLOCK_M 行、D 列的 tile。这是读取结果的局部形状，与整体视图大小不同。
+• [T#B#本次起点]：load(\[r0,0\]) 从第 r0 行、第 0 列开始取该形状的块。若把起点改为 \[r0+BLOCK_M,0\]，就向下移动一个 Q tile；返回形状仍为 \[BLOCK_M,D\]。
+[T#B,!c47f17#边界]：offsets 是每次 load 的参数，不是创建 descriptor 时固定的块起点。以上访问仍须满足该接口的布局、对齐和边界要求；本卡以 Triton 3.7.1 为准。</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -515,15 +544,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">descriptor 会自动保护当前 head 的边界吗？</t>
+          <t xml:space="preserve">Attention 的 Q/K/V descriptor 把多个 batch/head 展平成 \[BHN,D\]，每个 head 占 N 行。若一次 load 跨过当前 head 的末尾，却仍在整个 BHN 行视图之内，descriptor 会自动将越过这个 head 的位置补零吗？</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：只识别声明视图的边界；不会额外识别其中的逻辑 head 边界。
-• [T#B#跨 head]：batch/head 合并到行轴后，跨过当前 head 但仍在整个视图内的位置依然合法，可能读到下一 head。
-• [T#B#逻辑范围]：必须用当前 head 的起点与访问范围保证数据归属。
-[T#B,!c47f17#边界]：在默认 zero padding 且访问满足约束时，越过整个声明视图的位置补零，返回 tile 形状仍不变。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不会。descriptor 只判断坐标是否越过声明的整体视图，不知道其中哪 N 行属于当前逻辑 head。
+• [T#B#为何仍合法]：跨到下一 head 的行号只要仍小于 BHN，就还是 \[BHN,D\] 中的合法坐标。load 可能正常读到下一 head 的数据，而不会把它当成越界。
+• [T#B#需要保证的范围]：调用方必须正确计算当前 head 的基址，并限制本 program 的 token 扫描范围；batch/head 的逻辑隔离是索引设计的一部分。
+• [T#B#真正越界时]：在默认 zero padding 且访问满足其他约束的情况下，只有超出整个声明视图的元素才会补零。即使尾部有补值，返回 tile 的形状仍由 block_shape 决定。
+[T#B,!c47f17#边界]：自动处理内存视图越界，不等于自动实现 Attention 的 head 边界或 causal 规则；这些逻辑条件仍需由访问范围和 score mask 保证。</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -540,16 +570,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">K/V 补零为什么不能代替无效 key 的 mask？</t>
+          <t xml:space="preserve">Attention 处理不足一个 tile 的尾部 key 时，假设 descriptor 已把无效位置的 K 和 V 都补成零。能否省掉对这些 key 的 score mask，直接让 softmax 和 pV 计算整个 tile？</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：补零没有删除无效 key 在 softmax 分母中的贡献。
-• [T#B#零 K]：零 K 与 query 的点积为零，但零 score 的指数权重不是零；下面写的是取指数前的 score。
-[E##S_{ij}=0,\qquad e^{S_{ij}}=1\ne0]
-• [T#B#零 V]：V 补零只能消除该位置对加权分子的直接贡献，分母仍可能被它改变。
-[T#B,!c47f17#边界]：应屏蔽无效位置的 score，使其 softmax 权重为零；把 K/V 填成负无穷不能代替这个步骤。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。零 K/V 并没有把无效 key 从 softmax 的归一化集合中删除，它仍可能改变分母。
+• [T#B#零K的分数]：对有限 query，零 K 的点积为零，乘 scale 后 score 仍为零。但零分数的指数权重不是零。
+[E##S_{ij}=0\quad\Longrightarrow\quad e^{S_{ij}}=1]
+• [T#B#稳定化也不删除]：本卡用自然分数 S 说明，令 m_S=max(S)。减去最大值后，零分数的指数项为 exp(−m_S)，仍会计入分母；稳定化没有删除这个无效 key。若换成 exp2，则最大值也必须使用对应的换底标度。
+• [T#B#零V只影响分子]：零 V 使该项在加权分子中的直接贡献为零，但它仍占据分母，可能把真实 value 的输出权重压小。
+[T#B,!c47f17#边界]：应在 score/概率上按有效 key 条件屏蔽这些位置，使它们对归一化不贡献权重。也不能把 K/V 填成 −∞ 来代替 score mask，因为点积和乘法会产生不同的数值行为。</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -566,15 +597,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">descriptor 的 padding 能像 other 一样任意指定吗？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，普通 tl.load 可用 other 指定 masked 位置的替代值。若改用 TensorDescriptor 的 load，能否同样传入任意 other 值？可选的 padding 在哪里设置？</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能；该版本提供 zero 和 nan 两种预设，默认是 zero。
-• [T#B#参数位置]：host TensorDescriptor 使用 padding；device make_tensor_descriptor 使用 padding_option，策略在构造时指定。
-• [T#B#其他填充值]：需要其他值时，可加载后按有效位置替换，或使用普通带 mask 的 tl.load。
-[T#B,!c47f17#边界]：nan 仅适用于浮点数据；descriptor.load 没有任意 other 参数。本卡限定 Triton 3.7.1。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：descriptor 不提供任意 other 值；它在构造时选择预设的 zero 或 nan padding，默认是 zero。
+• [T#B#host构造]：host 侧 TensorDescriptor 使用 padding 参数，例如 padding="zero"。这项设置属于 descriptor，而不是每次 load 时单独给出的标量。
+• [T#B#device构造]：kernel 内 tl.make_tensor_descriptor 使用 padding_option 参数，提供同样的预设选择。nan 仅适用于浮点数据。
+• [T#B#其他替代值]：如果运算需要别的值，可以在 load 后根据有效位置条件替换，或者改用普通带 mask 和 other 的 tl.load。选择要满足所用接口的访问约束。
+[T#B,!c47f17#边界]：Attention 的无效 key 需要的是对 score/概率的语义屏蔽；改变 K/V 的越界填充值不能直接代替 softmax mask。本卡的 API 选项限定于 Triton 3.7.1。</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -591,17 +623,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">连续张量为什么仍可能不满足 TMA 对齐？</t>
+          <t xml:space="preserve">把一个 PyTorch 张量传给 Triton 3.7.1 的 NVIDIA TMA descriptor 前，为什么仅检查 is_contiguous() 不够？应怎样检查实际基址与 stride 的基础对齐条件，切片视图又会带来什么问题？</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：连续性不保证视图首地址对齐；实际基址和字节步长都需要检查。
-• [T#B#检查量]：A 是 tensor.data_ptr() 返回的视图首地址；e 是每元素字节数，s 是以元素计的 strides。
-[E##A\bmod16=0,\qquad s_{\mathrm{last}}=1,\qquad (s_ke)\bmod16=0\quad(k&lt;\mathrm{last})]
-• [T#B#偏移反例]：对齐的一维 FP16 张量取 x\[1:\]，视图仍连续，但首地址偏移两个字节，破坏 16 字节对齐。
-• [T#B#复制边界]：视图已经连续时，contiguous() 可原样返回，不能保证通过重新分配修复对齐。
-[T#B,!c47f17#边界]：这里是 NVIDIA TMA 路径的基础布局条件；满足它们仍不代表块形状或后续 dot 必然合法。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：连续性描述元素的排列关系，并不保证视图首地址满足 TMA 对齐；必须检查实际地址和以字节计的步长。
+• [T#B#需要的量]：设 A=tensor.data_ptr() 为当前视图第一个元素的地址，e 为每元素字节数，s_k 为第 k 维的元素 stride。descriptor 的 strides 参数以元素计，对齐条件则以字节计。
+[E##A\bmod16=0,\qquad s_{last}=1,\qquad (s_ke)\bmod16=0\quad(k&lt;last)]
+• [T#B#切片反例]：一个基址对齐的一维 FP16 张量取 x\[1:\] 后，视图仍可连续，但首地址向后移动 2 字节，从而破坏 16 字节对齐。必须检查传入视图的 data_ptr，而非原始存储的起点。
+• [T#B#contiguous的限制]：如果这个视图本来就连续，contiguous() 可以直接返回它，不会为了对齐自动分配新存储。因此调用 contiguous() 不能替代地址检查。
+[T#B,!c47f17#边界]：这里只列出本路径的基础布局条件。即使这些条件满足，也还需要核对 block_shape、设备支持及后续矩阵乘的限制。</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -618,16 +650,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">host descriptor 为何需要 pre-hook 更新块大小？</t>
+          <t xml:space="preserve">所学 Attention 的普通 FP16 路径中，D 表示每个 head 的特征维度。wrapper 在 host 侧先用 dummy_block 创建 TensorDescriptor，而 autotune 会尝试不同 BLOCK_M/BLOCK_N。为什么每次配置运行前必须由 pre-hook 更新 block_shape，不能指望 kernel 中的 _maybe_make_tensor_desc 自动改正确？</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：块大小必须匹配本次配置，而 kernel helper 会原样返回已有 descriptor。
-• [T#B#初始状态]：wrapper 先用 dummy_block 作为占位；这时还没有给每次候选配置准备正确的访问块形状。
-• [T#B#调用前更新]：候选配置的 pre-hook 按本次 BLOCK_M、BLOCK_N 更新 Q/O 与 K/V 的 block_shape。
-• [T#B#helper 分支]：_maybe_make_tensor_desc 仅在收到指针时构造；收到已有 descriptor 时，额外传入的 block_shape 不会覆盖它。
-[T#B,!c47f17#边界]：pre-hook、grid 与 kernel 内部形状必须使用同一配置；这是所学教程快照的调用安排。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：host 传入的已经是 descriptor，helper 会原样返回它；因此进入 kernel 前，它的块大小就必须与当前配置一致。
+• [T#B#占位阶段]：dummy_block 只是构造 descriptor 时的占位形状。实际一轮候选可能选择不同的 Q tile 行数 BLOCK_M 和 K/V tile 行数 BLOCK_N。
+• [T#B#pre-hook的职责]：运行每个候选前，把 Q/O descriptor 的 block_shape 改为 \[BLOCK_M,D\]，K/V 改为 \[BLOCK_N,D\]，使 load/store 的实际形状匹配该候选。
+• [T#B#helper两条路径]：收到普通指针时，helper 才使用 shape、strides、block_shape 构造 descriptor；收到已有 descriptor 时直接返回，额外传入的 block_shape 不会覆盖对象。
+[T#B,!c47f17#边界]：pre-hook、grid 和 kernel 内计算形状必须使用同一候选配置。这个问题来自所学教程的 host descriptor 调用方式，不能假设所有 descriptor 都必须采用 dummy_block。</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -644,15 +676,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5M2 与 FP16 的有效精度差在哪里？</t>
+          <t xml:space="preserve">比较 FP8 E5M2 和 FP16 的表示精度：前者为 1 位符号、5 位指数、2 位显式小数，后者为 1、5、10。固定同一个正规数指数区间，E5M2 相邻可表示数的间距是 FP16 的多少倍？为什么指数位数相同仍不代表精度相同？</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：同一正规指数区间内，E5M2 的相邻数间距是 FP16 的 256 倍。
-• [T#B#位数]：E5M2：1 位符号、5 位指数、2 位小数；FP16：1、5、10。
-[E##\operatorname{spacing}=2^{e-p},\quad 2^{e-2}/2^{e-10}=2^8=256]
-[T#B,!c47f17#边界]：比较限定在同一正规指数区间；相同指数位数不能推出同样精度。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：E5M2 的相邻间距是 FP16 的 256 倍；相同指数位数没有补回少掉的小数位。
+• [T#B#正规数模型]：在固定指数 e 的正规区间中，数值可写成符号×2^e×(1+f/2^p)，p 是显式小数位数。f 每增加 1，相邻数就相差 2^(e−p)。
+[E##\frac{2^{e-2}}{2^{e-10}}=2^8=256]
+• [T#B#含义]：E5M2 只有 2 位显式小数，同一个区间内可表示的点更稀疏。把 FP16 数值转为它时，即使不发生范围溢出，也可能产生更大的舍入误差。
+[T#B,!c47f17#边界]：这里比较的是同一正规指数区间的间距，不覆盖零、非正规数或特殊值。指数位数主要关联范围，小数位数影响局部表示分辨率。</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -669,15 +702,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">两次逆 permute 中间的 contiguous 改变了什么？</t>
+          <t xml:space="preserve">所学 FP8 Attention 为 V 调整布局：B/H 分别是 batch/head 数，N 是 token 数，D 是特征维。从连续的 \[B,H,N,D\] 张量出发，先 permute 成 \[B,H,D,N\] 并 contiguous()，再用逆 permute 恢复 \[B,H,N,D\]。最终 shape 已恢复，为什么存储布局仍然改变？删掉中间 contiguous() 又会怎样？</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它先按转置后的轴顺序复制存储；再恢复逻辑 shape 时，stride 已经改变。
-• [T#B#本课 V]：连续 \[B,H,N,D\] 先变 \[B,H,D,N\] 并复制，再变回 \[B,H,N,D\]：末两维 stride 从 \[D,1\] 变为 \[1,N\]。
-[E##\operatorname{offset}(g,n,d):\quad gND+nD+d\ \longrightarrow\ gND+dN+n]
-[T#B,!c47f17#边界]：删掉中间复制，互逆 permute 恢复原 shape 和 stride；对原连续张量，最后再 contiguous 通常无需搬动。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：中间 contiguous() 按转置后的轴顺序复制了数据；逆 permute 只恢复逻辑轴顺序，不会把这次复制后的存储重新排列回去。
+• [T#B#原布局]：连续 \[B,H,N,D\] 的末两维 stride 是 \[D,1\]，同一个 token 的 D 个特征相邻。令 g=bH+h，则元素 (g,n,d) 的线性偏移为 gND+nD+d。
+• [T#B#复制后]：在 \[B,H,D,N\] 下做 contiguous 后，同一个特征的 N 个 token 相邻。再恢复逻辑 shape，末两维 stride 变成 \[1,N\]，元素偏移为 gND+dN+n。
+[E##gND+nD+d\ \longrightarrow\ gND+dN+n]
+• [T#B#删除中间复制]：仅连续做两次互逆 permute 会把 shape 和 stride 都恢复，底层存储没有搬动。对于原本连续的张量，最后再调用 contiguous 通常也无需复制。
+[T#B,!c47f17#边界]：判断布局必须同时看 shape、stride 和是否发生实际复制。此处解释的是所学 V 重排；后续转换为 FP8 的 dtype 操作，与轴布局变化是另一件事。</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -694,15 +729,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">比较反向结果怎样保证输入条件一致？</t>
+          <t xml:space="preserve">验证两个 Attention 实现的反向结果时，参考实现先调用 backward(dout)，然后再运行被测实现。除了 Q/K/V 相同，还必须固定哪些输入条件？为什么保存参考梯度后要清空叶子张量的 .grad？</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：参考实现和被测实现必须对同一输入、同一上游 dO 求导。
-• [T#B#固定]：Q/K/V、causal、scale 和 dO 都一致；不同 dO 对应不同的加权输出损失。
-• [T#B#清理]：保存参考梯度后清空叶子 .grad，避免后一次 backward 累加到前一次结果上。
-[T#B,!c47f17#边界]：条件不同产生的梯度差异，不能直接归因于 kernel 错误。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：两边必须对同一计算问题、同一上游梯度求导，并避免后一次 backward 把结果累加到已有梯度上。
+• [T#B#同一前向问题]：Q/K/V、causal 开关与原始 scale 都要相同，否则前向函数本身就不同。
+• [T#B#同一dout]：dout 即 dO，决定损失对输出各元素的加权。可把 backward(dout) 理解为对固定 dout 的标量 L=Σ(O*dout) 求导；换一个 dout，得到的梯度通常也会变。
+• [T#B#保存再清空]：先保存参考的 dQ/dK/dV，再清空对应叶子张量的 .grad。PyTorch 的 backward 会累计叶子梯度，否则第二次读到的可能是两次结果之和。
+[T#B,!c47f17#边界]：输入条件或梯度累计状态不同，得到的差异不能直接归因于被测 kernel 错误。比较前向 O 一致，也不能替代对上游 dO 的一致性检查。</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -719,15 +755,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">反向 FLOP 系数 2.5 说明什么？</t>
+          <t xml:space="preserve">所学 Attention benchmark 用前向 FLOP 数乘 2.5 来估算反向工作量。这里 FLOP 指浮点运算次数，B/H/N/D 分别是 batch、head、token 和特征维。2.5 的来源是什么，它能否预测反向耗时也是前向的 2.5 倍？</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它是 benchmark 对主要矩阵乘工作量的估算比例，不是耗时比例。
-• [T#B#估算依据]：前向主要有 QKᵀ 与 PV 两次矩阵乘，约 4BHN²D FLOP；反向按五次主要矩阵乘建模，得到 5/2。
-• [T#B#口径边界]：实际实现还会在不同梯度路径重复重算；causal 乘 0.5 也只是近似，所以报告值不是逐指令实际 FLOP 统计。
-[T#B,!c47f17#边界]：不能据此断定反向耗时为前向的 2.5 倍，耗时仍须测量。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：2.5 是主要矩阵乘工作量的报告模型：反向按五次、前向按两次估算，因此得到 5/2；它不是耗时预测。
+• [T#B#前向口径]：QKᵀ 与 PV 各有约 BHN²D 次乘加，按一次乘加计两个 FLOP，合计约 4BHN²D。
+• [T#B#反向口径]：benchmark 用五次主要矩阵乘来代表反向，相对前向两次形成 2.5 系数。它是一种统一报告口径，不是逐条核算该 kernel 执行的所有指令。
+• [T#B#实际实现]：不同梯度路径还可能重复重算概率相关项，并包含归约、指数、读写等工作。causal 把工作量乘 0.5 也只是近似。
+[T#B,!c47f17#边界]：耗时同时受数据搬运、并行度、资源与执行组织影响，必须实际测量。不能由这个系数断言反向必定慢 2.5 倍，也不能把报告 FLOP 当作精确的硬件指令数。</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -744,15 +781,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">相同 Q 行为何不总产生相同 Attention 输出？</t>
+          <t xml:space="preserve">在同一个 Attention head 内，所有 query 向量都相同，K/V 和 scale 固定。非 causal 时，各行 O 与 M 为什么在数学上相同？改成 causal 后，这个“所有行相同”的结论为什么不能直接沿用？M 表示每行归一化分母的 base-2 对数。</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：还要有效 key 集合相同；相同 Q 只保证对同一个 key 的 score 相同。
-• [T#B#non-causal]：同一 head、同一 scale 下，所有 Q 相同且都访问全部 K/V，因此数学上的 O/M 行相同。
-• [T#B#causal]：不同 query 的可见前缀不同，不能推出 O/M 行相同；O 仍可能因特殊 V 恰好相同。
-[T#B,!c47f17#边界]：causal 包括当前位置自身。这里是数学不变量，数值实现仍有舍入误差。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：相同 Q 保证对同一个 key 的分数相同；还需要每行使用同一组有效 key，才能推出相同的权重、O 和 M。
+• [T#B#非causal]：每个 query 都访问完整 K/V，因此分数序列和归一化集合都相同。softmax 概率相同，加权相同的 V 后输出也相同，分母的 log₂ 即 M 同样相同。
+• [T#B#causal]：第 i 行只访问 j≤i 的前缀，包含自身。即使对共同 key 的分数一样，参与归一化的集合仍随 query 位置改变，所以不能继续推断所有 O/M 行相同。
+• [T#B#输出并非必然两两不同]：有效集合变化通常会使 O 变化，但特殊的 V 仍可能使某些行输出相同；例如所有 value 相同，归一化后的加权和仍可能相同。
+[T#B,!c47f17#边界]：这里讨论同一 head、同一 scale 和一致输入下的数学关系。浮点实现会有舍入误差；不能把“通常变化”加强成“任意两行必定不同”。</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-06-fused-attention-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-06-fused-attention-technical-qa.xlsx
@@ -56,19 +56,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 分数 → 沿 key 归一化 → 加权 V</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 全貌、符号与精度</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">普通 Attention 会把 N 个 query 对 N 个 key 的分数矩阵 S，以及 softmax 概率矩阵 P，写入全局显存。FlashAttention 改为按块计算时，主要避免了什么开销？QKᵀ 和 PV 的计算量是否也因此消失？</t>
+          <t xml:space="preserve">普通 Attention 按 S=sQKᵀ、P=softmax(S)、O=PV 逐步计算（N 个 query、N 个 key，s 为缩放系数），每一步都先得到完整结果再交给下一步。FlashAttention 改为按块计算后，省掉的是哪一类开销，哪一类主要工作仍然保留？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：主要省去完整 N×N 中间矩阵的物化及其显存读写；QKᵀ 和 PV 的主要计算仍然需要完成。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：省掉的是完整 N×N 分数矩阵与概率矩阵的物化，以及它们在全局显存中的写入和读回；QKᵀ 与 PV 两个主要矩阵乘仍要完成。
 • [T#B#普通路径]：先写出完整 S，再读取它求 softmax 并写出 P，最后读取 P 与 V 相乘，会产生大量中间数据的存储和搬运。
 • [T#B#分块路径]：固定一个 Q 块，逐块读取 K/V；分数和指数权重只作为当前块的临时量，旧块的影响由少量逐行统计量及输出累加器保留。
 • [T#B#计算边界]：仍需对相关 query–key 对计算分数，并把权重作用到 V。对完整非因果注意力，主要矩阵乘工作量仍随 N²D 增长。
@@ -82,14 +82,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-19 · 不物化 N×N；仍计算 QKᵀ、PV</t>
+          <t xml:space="preserve">Attention 学习记录 09-19 · 不物化 S/P 的要点</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">在所学 FP16 Attention 前向中，输入 Q/K/V 的形状是 \[B,H,N,D\]：B 为 batch 数、H 为 head 数、N 为 token 数、D 为每个 head 的特征维。BLOCK_M 是一个 Q tile 的行数。grid=(ceil(N/BLOCK_M),B×H,1) 怎样把计算和最终输出分给各 program？</t>
+          <t xml:space="preserve">在 Triton 官方 fused-attention 教程（快照版）的 FP16 前向中，输入 Q/K/V 的形状是 \[B,H,N,D\]：B 为 batch 数、H 为 head 数、N 为 token 数、D 为每个 head 的特征维。BLOCK_M 是一个 Q tile 的行数。grid=(ceil(N/BLOCK_M),B×H,1) 怎样把计算和最终输出分给各 program？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -98,7 +98,7 @@
 • [T#B#第0轴]：program_id(0) 选择 Q tile。编号为 p 的 tile 对应 head 内从 p×BLOCK_M 开始的 query 行。
 • [T#B#第1轴]：program_id(1) 选择合并后的 batch/head 编号 g；可由 b=g//H、h=g%H 还原到具体输入切片。
 • [T#B#内部循环]：K/V 的分块扫描在同一个 program 内完成。扫描多少轮与启动多少个 program 是不同概念；这个前向不是每个 Q×K 块都启动一个独立 program。
-• [T#B#第2轴]：尾部 1 表示第三轴只有一个位置。本实现没有使用该轴，把 grid 写成前两维即可表达相同分工。
+• [T#B#第2轴]：尾部 1 表示第三轴只有一个位置。该教程没有使用这根轴，把 grid 写成前两维即可表达相同分工。
 [T#B,!c47f17#边界]：grid 轴的业务含义来自 kernel 如何使用 program_id。它们不是 Triton 预先规定的 query、batch、head 轴。</t>
         </is>
       </c>
@@ -109,7 +109,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 所学源码快照 · Q tile × batch/head；K/V 在内部扫描</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 全貌、符号与精度</t>
         </is>
       </c>
     </row>
@@ -136,23 +136,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-19／09-24 · 所学源码快照 · 先 gN，再加局部 token</t>
+          <t xml:space="preserve">Attention 学习记录 09-19 · K descriptor 行号纠错；09-24 · TensorDescriptor、边界与启动准备</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">分块 Attention 前向中，一个 Q tile 有 B_M 个 query；本轮 K/V tile 有 B_N 个 key/value；每个 value 有 D 个特征。指数权重块的形状是 \[B_M,B_N\]。累加加权 V 的 acc 应是什么形状，为什么不能因 B_M 恰好等于 D 就把它理解成 \[B_M,B_M\]？</t>
+          <t xml:space="preserve">分块 Attention 前向中，一个 program 负责 B_M 个 query；本轮读入 B_N 个 key/value，每个 value 是 D 维特征向量；当前块的未归一化指数权重 p 形状为 \[B_M,B_N\]。跨多轮 K/V 累计 pV 的输出分子 acc 应是什么形状？请用乘加时被归约和被保留的轴说明。</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：acc 的形状是 \[B_M,D\]：每个 query 保留一个 D 维加权 value 向量。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：acc 的形状是 \[B_M,D\]：乘加归约掉本轮的 key 轴 B_N，保留 query 轴 B_M 和特征轴 D，每个 query 对应一个 D 维加权 value 向量。
 [E##\underbrace{p}_{B_M\times B_N}\ \underbrace{V}_{B_N\times D}\ \longrightarrow\ \underbrace{acc}_{B_M\times D}]
-• [T#B#归约轴]：乘加时对本轮的 key/value 索引求和，B_N 这一轴被归约；保留下来的是 query 轴 B_M 和 value 特征轴 D。下一轮 K/V 继续加到同一个 acc。
+• [T#B#归约轴]：乘加时对本轮的 key/value 索引求和，B_N 这一轴被消去；下一轮 K/V 的贡献继续加到同一个 acc，形状不变。
 • [T#B#逐行统计]：运行最大值 m、指数和 l、重标定系数 alpha 都是一 query 一个值，所以形状为 \[B_M\]。给 acc 重标定时用 alpha\[:,None\] 沿 D 轴广播。
-[T#B,!c47f17#边界]：B_M=64、D=64 只是数值偶合，不能改变轴的含义。换成 B_M=32、D=64 时，acc 仍然是 \[32,64\]。</t>
+[T#B,!c47f17#边界]：形状由轴的含义决定，不能看数值：即使 B_M 与 D 都取 64，acc 的两根轴仍分别是 query 和特征；B_M=32、D=64 时 acc 为 \[32,64\]。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 消去 key；留下 query × feature</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 全貌、符号与精度</t>
         </is>
       </c>
     </row>
@@ -190,24 +190,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-19／09-24 · 新最大值 → 同缩放 → 合并 → acc/l</t>
+          <t xml:space="preserve">Attention 学习记录 09-19 · 第二轮保留量纠错；09-24 · 前向在线状态与源码语义</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">所学 Attention 前向将每个 query 的在线状态初始化为 m=−∞、l=1、acc=0。其中 m 是 exp2 输入域分数的运行最大值。假设首块至少有一个有效 key，且所有有效 score 都有限（无效位置可被 mask 为 −∞），为什么初始 l=1 不会使 softmax 分母多出 1？改成 l=0 是否也可行？</t>
+          <t xml:space="preserve">某个分块 Attention 前向把每个 query 的在线状态初始化为 m=−∞、l=1、acc=0，其中 m 是 exp2 输入域分数的运行最大值。假设首块至少有一个有效 key，有效 score 都有限，无效位置被 mask 为 −∞。为什么初始的 l=1 不会进入最终分母？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：首块使新最大值变为有限数，因此重标定系数为 0，初始 l 的有限值会被消去；在这些条件下，l 初始为 0 或 1 都可行。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 m 从 −∞ 开始：首块使最大值变为有限数，重标定系数 alpha=2^(−∞−m_new)=0，初始 l 被乘 0 消去。所以在这些条件下 l 初值取 0 或 1 都可以，关键是 m 必须从 −∞ 开始。
 • [T#B#符号]：令 x_j 表示尚未取指数、已换底为 exp2 标度的有效 key 分数，m_new 是加入首块后的有限最大值；l₀ 是初始的有限分母状态。
 [E##\alpha=2^{-\infty-m_{new}}=0,\qquad l_{new}=\alpha l_0+\sum_j2^{x_j-m_{new}}]
-• [T#B#为什么选m很关键]：这里能消去初值，依赖于 m 的初始值是 −∞。如果误把 m 初始化为 0，而首块所有分数都小于 0，新最大值可能仍是 0，alpha=1，初始 l=1 就会残留。
-• [T#B#异常值边界]：l=1 并不能修复 inf−inf 产生的 NaN；首块全无效或包含异常无穷值时，必须另行定义和处理数值语义。NaN 也不会因为乘 0 自动消失。
-[T#B,!c47f17#边界]：代码行为能解释这种初始化在合法输入下成立，但没有足够证据据此断言作者选择 1 是为了防止某种异常。</t>
+• [T#B#m初值的作用]：若误把 m 初始化为 0，而首块分数都小于 0，新最大值仍是 0，alpha=1，初始 l=1 会残留在分母里；若误写成 +∞，首次重标定就出现 inf−inf，得到 NaN。
+• [T#B#异常值]：l=1 修复不了 inf−inf 产生的 NaN；首块全无效或含 +∞ 时，必须另行定义和处理数值语义，NaN 乘 0 仍是 NaN。
+[T#B,!c47f17#边界]：这只说明该初始化在上述有效输入下成立；没有证据表明选择 1 是为了防止某种异常。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -217,7 +217,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 有限首块 → alpha=0 → 初始 l 消失</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 前向在线状态与源码语义；实践修改与 A4 独立解释</t>
         </is>
       </c>
     </row>
@@ -244,17 +244,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 过去／对角／未来</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 前向在线状态与源码语义</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Triton 官方 fused-attention 教程（快照版）的前向 kernel 有一个编译期参数 STAGE，causal 时取 3、non-causal 时取 1；它的 autotune 候选配置里另有 num_stages。这两个名字相近的参数分别控制什么？</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：STAGE 决定前向扫描哪些 key 区段，管的是计算范围和 mask；num_stages 是软件流水线深度，属于执行配置，不改变扫描哪些 key。
+• [T#B#外层位掩码]：外层 STAGE 按位使用：3=0b11，STAGE&amp;1 与 STAGE&amp;2 都非零，于是先以内层模式 1 扫描过去区、再以模式 2 扫描对角区，两次调用接续同一组 m/l/acc；non-causal 的 1 只打开第一位，以内层模式 3 扫描整段序列。
+• [T#B#两个“3”]：传给 _attn_fwd_inner 的 1/2/3 是具体扫描模式（过去／对角／全序列），与外层位掩码同名不同义：外层 3 表示两段都执行，内层 3 表示扫描全序列。
+• [T#B#num_stages]：num_stages 与 num_warps、maxnreg 同属执行与资源配置：它设定编译器软件流水线的深度，影响性能和资源占用，但不是越大越好。
+[T#B,!c47f17#边界]：num_stages 不是 causal 的 STAGE：调整它不会改变 STAGE 决定的扫描区段和有效 key 范围。</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAGE 管扫描哪些段；num_stages 管流水线多深</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-19 · STAGE 位掩码问题；09-24 · 前向在线状态与源码语义；FP8、布局与执行配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Attention 前向采用 exp2，令 x_j=S_j/ln2，其中 S_j 是已乘原始 scale 的点积分数。它为一行有效 key 保存 m=max(x_j)、l=Σ2^(x_j−m)，并只把 M=m+log₂(l) 留给反向。为什么反向用 2^(x_j−M) 就能恢复概率，且没有丢掉减最大值的稳定化效果？</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：M 是整行原始指数和的 log₂；减去 M 同时完成了减最大值和除以归一化分母。
 [E##M=m+\log_2l=\log_2\sum_j2^{x_j}]
@@ -264,104 +290,104 @@
 [T#B,!c47f17#边界]：这个结论限定在有效位置以及前后向使用一致分数的数学运算；全屏蔽行、非有限输入需要单独处理，浮点也仍可能舍入或下溢。M 是 log-sum-exp，不能再把它误认成行最大值 m。</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">先稳定求和；再保存 log 分母</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-19／09-24 · 先稳定求和；再保存 log 分母</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在所学 FP16 Attention 前向实现中，Q/K/V 以 FP16 存储，输出 O 也需要返回 FP16。沿 QKᵀ、softmax 在线统计、pV 到 O/M 写回这条路径，各阶段使用什么精度，关键转换发生在哪里？</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-19 · 加回 m 的问题；09-24 · 全貌、符号与精度</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 Triton 官方 fused-attention 教程（快照版）的 FP16 前向中，Q/K/V 以 FP16 存储，输出 O 也需要返回 FP16。沿 QKᵀ、softmax 在线统计、pV 到 O/M 写回这条路径，各阶段使用什么精度，关键转换发生在哪里？</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：矩阵乘用低精度操作数配合 FP32 累加，归一化与在线状态保留 FP32；中途 pV 前和最终 O 写回前都会发生降精度转换。
 • [T#B#QKᵀ与score]：Q 和 K 是 FP16 操作数，点积累加结果为 FP32。后续缩放、最大值、减最大值和指数权重计算使用 FP32，保护归约和指数相关的数值计算。
 • [T#B#在线状态]：每个 query 的最大值 m、指数和 l，以及 D 维输出分子 acc 都保留 FP32，使跨多个 K/V 块的合并不必每轮舍入到 FP16。
-• [T#B#pV之前]：p 表示当前块的未归一化指数权重。先用 FP32 p 求分母增量，再把 p 转为 FP16，与 FP16 V 相乘；乘积继续累计到 FP32 acc。
+• [T#B#pV之前]：p 表示当前块的未归一化指数权重。先用 FP32 p 求分母增量，再把 p 转为 FP16，与 FP16 V 相乘；乘积继续累计到 FP32 acc。这次转换不可省：在 Triton 3.7.1 的这条路径上，tl.dot 的两个操作数要同型，FP32 p 不能直接与 FP16 V 相乘。
 • [T#B#输出]：最后 acc/l 得到归一化输出，O 写回时转成 FP16；供反向重建概率的 M=m+log₂l 仍以 FP32 保存。
-[T#B,!c47f17#边界]：这是该实现的精度安排。调用者看到的输入或输出 dtype，不能代表每一步内部运算精度；也不能概括成“只有最终 O 才转换精度”。</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+[T#B,!c47f17#边界]：这是该教程的精度安排。调用者看到的输入或输出 dtype，不能代表每一步内部运算精度；也不能概括成“只有最终 O 才转换精度”。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">低精度乘法输入；高精度统计与累加</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 所学源码快照 · 低精度乘法输入；高精度统计与累加</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 前向中，p 是 FP32 的未归一化指数权重块，l 要累加每行的 sum(p)；另一路会把 p 转成 FP16 后与 FP16 V 做矩阵乘。如果把 sum(p) 移到 p 转 FP16 之后，即使仍用 FP32 累加，能保证分母结果不变吗？</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能保证。FP16 转换已经改变了参与求和的权重，FP32 累加只能更准确地累加这些舍入后的值。
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 全貌、符号与精度；实践修改与 A4 独立解释</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 前向中，p 是 FP32 的未归一化指数权重块：一路对每行求 sum(p) 累加到分母 l，另一路把 p 转成 FP16 后与 FP16 V 做矩阵乘。若把 sum(p) 改到 p 转成 FP16 之后再算，并且仍用 FP32 累加，分母会受什么影响？请从误差产生的位置解释。</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：分母可能改变：转成 FP16 时的舍入已经发生在求和的输入上，FP32 累加只能更准确地加这些舍入后的值，找不回丢失的低位。
 • [T#B#原顺序]：先对尚未降精度的 FP32 权重求行和，用于更新 l；然后仅为 pV 的矩阵乘把 p 转成 FP16。分母因此保留了转换前的权重信息。
 • [T#B#交换后]：若先转换，传给求和的是 round_fp16(p)，而不是原始 p。即使累加器是 FP32，也无法知道每个元素在转换中丢失了多少低位。
 • [T#B#误差位置]：高精度累加主要减少累加过程引入的误差，不能撤销累加开始前已经发生的输入量化误差。这就是要分别考虑操作数和累加器精度的原因。
-[T#B,!c47f17#边界]：并非每组输入都会产生可见差异，例如恰好能被 FP16 精确表示的权重可能一致；但两个顺序不是普遍数值等价的改写。</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+• [T#B#迁移（延伸）]：设计其他算子时同样要分开判断存储、操作数、累加器和输出 dtype：先明确误差与数值范围，识别指数、长归约等敏感环节，再决定低精度存储与转换位置，最后对照可信参考验证数值与性能。通用的是这套判断方法，不是固定的 dtype 配方。
+[T#B,!c47f17#边界]：并非每组输入都会出现可见差异，例如恰好能被 FP16 精确表示的权重结果一致；但两种顺序不是普遍数值等价的改写，也不能凭输入或输出 dtype 推断内部精度。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">先保住输入信息，再谈累加精度</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 先保住输入信息，再谈累加精度</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">阅读或设计一个新的深度学习算子时，输入和输出可能使用 FP16，但内部还有矩阵乘、长归约或指数运算。应怎样决定各阶段的精度，而不是凭输入 dtype 猜测全部内部计算类型？</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先确定允许的数值误差和输入范围，再把精度用在误差容易累积或放大的环节，最后用实验核对数值与成本。
-• [T#B#数值要求]：了解输入可能的大小、动态范围以及输出可接受的误差。有限表示范围可能造成溢出或下溢；有限有效位数可能使舍入误差累积。
-• [T#B#分开选择]：分别判断存储 dtype、实际操作数 dtype、累加器 dtype 和输出 dtype。它们可以不同，例如低精度矩阵乘操作数与高精度累加器配合。
-• [T#B#转换位置]：长归约、指数和归一化通常值得单独检查。明确在哪里升精度、在哪里允许降精度；高精度累加无法弥补早先已经丢失的输入信息。
-• [T#B#验证]：先对照可信参考验证正常与边界输入的误差，再测实际速度和存储收益。只有同时满足所需准确性与成本目标，精度配置才有依据。
-[T#B,!c47f17#边界]：通用的是这套判断方法，不是一套所有算子都适用的 dtype 配方。单凭“输出为 FP16”或“文档没有特别说明”，都不能推断内部始终是 FP16 或 FP32。</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">数值要求 → 敏感环节 → 转换位置 → 验证</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 数值要求 → 敏感环节 → 转换位置 → 验证</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 前向在线状态与源码语义；全貌、符号与精度</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">阅读所学 Attention 源码时，会看到前向 kernel 内多次调用 _attn_fwd_inner，也会看到反向先启动 preprocess、再启动主 backward。它们分别怎样传递计算状态？为什么不能把每个 @triton.jit 函数调用都当成独立的 kernel launch？</t>
+          <t xml:space="preserve">Triton 官方 fused-attention 教程（快照版）的反向不保存前向算出的概率矩阵 P：前向末尾只为每个 query 留一个统计量 M，反向再按块用 Q/K 与 M 重算 P。输入有 B 个 batch、H 个 head，每个 head N 个 token。这个设计省下了什么，又多付出了什么？</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：用一部分重复计算换掉 N² 量级的存储：不再保存、写出和读回每个 head 的 N×N 概率，只保存线性大小的 M；代价是反向要重新计算分数和概率。
+• [T#B#省下的存储]：完整 P 为 \[B,H,N,N\]，M 只有 \[B,H,N\]。以 \[B,H,N,D\]=\[2,4,128,64\] 为例，P 有 2·4·128²=131072 个元素，M 只有 2·4·128=1024 个；两者相差 N 倍，N 越大差距越大。
+• [T#B#多付的计算]：反向要重新计算 QKᵀ 并取指数来重建 P。教程 benchmark 的 FLOP 模型写作 2.0(bwd)+0.5(recompute)：dV、dP、dQ、dK 四个反向矩阵乘之外，再记一次重算的 QKᵀ，合计约为前向的 2.5 倍。
+• [T#B#实际执行]：该实现的 dK/dV 与 dQ 两条路径还各自重算 score 和 dP，存在重复计算；2.5 是约定的计算量模型，不是硬件实际执行的运算次数。
+[T#B,!c47f17#边界]：这是用计算换存储与显存读写的取舍，不是性能保证：是否更快要实测，2.5 也不能当作反向耗时相对前向的倍数。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">存 O(N) 的 M，重算 O(N²) 的 P；省存储，多计算</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-19 · 只存行统计量的要点；09-24 · 正确性与 benchmark 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阅读 Triton 官方 fused-attention 教程（快照版）的源码时，会看到前向 kernel 内多次调用 _attn_fwd_inner，也会看到反向先启动 preprocess、再启动主 backward。它们分别怎样传递计算状态？为什么不能把每个 @triton.jit 函数调用都当成独立的 kernel launch？</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：前向 inner 调用在同一个 kernel/program 内接续局部在线状态；反向的两个独立 Triton launch 则通过全局 Delta 缓冲区传递数据。
 • [T#B#前向helper]：_attn_fwd_inner 是 JIT 辅助函数。它更新当前 Q tile 的 m、l、acc，并返回新状态；外层必须按返回顺序重新绑定变量，后续区域才能继续之前的累加。
@@ -370,78 +396,78 @@
 [T#B,!c47f17#边界]：反向 wrapper 还包含 K 的预缩放等操作。因此“两次 Triton kernel 启动”只是在描述这两个显式 launch，不代表整个反向恰好只有两项 GPU 操作。</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">局部返回状态；全局传递 Delta</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 所学源码快照 · 局部返回状态；全局传递 Delta</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 全貌、符号与精度；实践修改与 A4 独立解释</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t xml:space="preserve">对一个 head，前向为 S=sQKᵀ、P=softmax_key(S)、O=PV；s 是固定缩放系数，Q/K/V 为 \[N,D\]。损失传来同形状的上游梯度 dO 后，如何依次算出 dP、分数梯度以及 dQ/dK/dV？</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：沿前向的相反方向：先从 O=PV 回传到 P/V，再通过每行 softmax 回传到 S，最后通过缩放点积回传到 Q/K。
 • [T#B#记号]：dP 表示损失对概率 P 的梯度；令 G=∂L/∂S，避免把“对自然分数 S 的梯度”与某种源码临时变量混淆。S、P、dP、G 都是 \[N,N\]。
 [E##dP=dOV^{\mathsf T},\qquad dV=P^{\mathsf T}dO]
-[E##\Delta_i=\sum_jP_{ij}dP_{ij},\qquad G_{ij}=P_{ij}(dP_{ij}-\Delta_i)]
+[E##\Delta_i=\sum_jP_{ij}dP_{ij}=\sum_dO_{id}\,dO_{id},\qquad G_{ij}=P_{ij}(dP_{ij}-\Delta_i)]
 [E##dQ=sGK,\qquad dK=sG^{\mathsf T}Q]
-• [T#B#形状与分块]：dQ/dK/dV 都回到 \[N,D\]。实现可以在需要时按块用 Q/K 和保存的 M 重建 P，再累计这些公式对应的梯度，无需保存完整 N×N 概率。
+• [T#B#形状与分块]：dQ/dK/dV 都回到 \[N,D\]。实现用右式 Σ_d O_id·dO_id 从保存的 O 与传入的 dO 算出 Δ，再按块用 Q/K 和保存的 M 重建 P、累计这些梯度，无需保存完整 N×N 概率。
 [T#B,!c47f17#边界]：causal 模式中，无效 query–key 位置的 P 和 G 均不贡献梯度。这里求的是对 Q/K/V 的梯度，假设 s 固定。</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">O → P/V → S → Q/K</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · O → P/V → S → Q/K</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 反向统计量、归约与缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">Attention 反向重建一个概率 tile 时，M 和 Delta 都是“每个 query 一个值”的统计量。如果概率 tile 有时按 \[Bq,Bk\]（query×key）存放，有时按 \[Bk,Bq\]（key×query）存放，这两个向量应怎样广播才能对应到正确 query？</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：先找出概率 tile 的 query 轴，让每个统计量保持与对应 query 的绑定，再沿 key 轴复制。
 • [T#B#query在行]：对于 \[Bq,Bk\]，M 与 Delta 的形状都是 \[Bq\]。用 M\[:,None\]、Delta\[:,None\] 得到 \[Bq,1\]，向同一 query 的各个 key 列广播。
 • [T#B#query在列]：对于 \[Bk,Bq\]，query 是第二轴。用 M\[None,:\]、Delta\[None,:\] 得到 \[1,Bq\]，向各个 key 行广播。
-• [T#B#为什么会不同]：所学 dQ 路径固定 Q 并扫描 K/V，使用 query×key 布局；dK/dV 路径固定 K/V 扫描 Q，使用转置的 key×query 布局。
+• [T#B#为什么会不同]：该教程的 dQ 路径固定 Q 并扫描 K/V，使用 query×key 布局；dK/dV 路径固定 K/V 扫描 Q，使用转置的 key×query 布局。
 [T#B,!c47f17#边界]：不能按变量名照抄另一路的 \[:,None\] 或 \[None,:\]。M 用来恢复概率，Delta 用来计算 softmax 梯度，但它们都必须跟随 query 轴。</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">统计量属于 query；广播跨 key</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 统计量属于 query；广播跨 key</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 反向统计量、归约与缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t xml:space="preserve">分块计算 Attention 的 dK/dV 时，同一个 key 会接收多个 query 的梯度贡献。什么样的 program 分工可以在写回这些梯度时不用 atomic？如果把同一输出块的贡献拆给两个 program，为什么普通 store 不够？</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：让一个 program 算齐某个 dK/dV 输出块的全部贡献，并让它成为该块唯一的写入者，就无需跨 program 的 atomic 累加。
 • [T#B#完整归约]：固定一个 K/V tile 后，负责它的 program 扫描所有有效 query 块，在自己的累加器中把各块贡献求和。扫描结束后只写回一次完整结果。
@@ -450,24 +476,24 @@
 [T#B,!c47f17#边界]：无需 atomic 的前提是“单个 program 完成完整归约且独占输出”。不能把它推广为所有 Attention 反向实现都不需要同步或归约。</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">完整归约 + 独占输出</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-19／09-24 · 完整归约 + 独占输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-19 · dK/dV 无需 atomic 的要点；09-24 · 反向统计量、归约与缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve">causal Attention 规定 query i 只能使用 key j≤i。反向计算时，固定一个 query 来求 dQ，与固定一个 key 来求 dK/dV，分别要汇总哪一侧 token 的贡献？为什么扫描方向看起来相反？</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：它们来自同一个因果约束，只是固定的索引不同：固定 i 时取 j≤i，固定 j 时取 i≥j。
 • [T#B#dQ的归约]：求 query i 的 dQ，需要汇总它看得到的 key，所以扫描该位置及此前的 key：0≤j≤i。未来 key 从未参与其前向输出，没有对应贡献。
@@ -476,24 +502,24 @@
 [T#B,!c47f17#边界]：两种范围都包含当前位置自身。不要把前向的“query 看过去 key”机械改写成“key 的梯度也只看过去 query”。</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">dQ 看过去 key；dK/dV 看后续 query</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-19 · dQ 看过去 key；dK/dV 看后续 query</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">所学 Attention 反向先把 K 预缩放为 K̃=(s/ln2)K。令 G=P⊙(dP−Delta) 表示损失对自然分数 S=sQKᵀ 的梯度。为什么 dQ 路径用 K̃ 累加后要乘 ln2，而 dK 路径用原始 Q 累加后要乘 s？</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-19 · causal 反向扫描范围的要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 官方 fused-attention 教程（快照版）的反向先把 K 预缩放为 K̃=(s/ln2)K。令 G=P⊙(dP−Delta) 表示损失对自然分数 S=sQKᵀ 的梯度。为什么 dQ 路径用 K̃ 累加后要乘 ln2，而 dK 路径用原始 Q 累加后要乘 s？</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：末尾系数是在补回各路径尚缺或多带的缩放；两条路径输入中的 scale 并不相同。
 • [T#B#dQ路径]：数学目标是 dQ=sGK。使用预缩放 K̃ 后，临时结果为 GK̃=(s/ln2)GK，已含 s，却多了 1/ln2，因此最后乘 ln2。
@@ -503,135 +529,109 @@
 [T#B,!c47f17#边界]：必须追踪这个版本 wrapper 与 kernel 实际使用的张量。这里的 G 是对自然分数 S 的梯度；若另一实现选择不同表示域或预缩放位置，不能照搬末尾系数。</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">追踪预缩放；不要机械套同一系数</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 所学源码快照 · 追踪预缩放；不要机械套同一系数</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">使用 Triton TensorDescriptor 按块读取张量时，base、shape、strides、block_shape 和 load(offsets) 分别决定什么？例如 B/H/N/D 分别表示 batch 数、head 数、token 数和特征维，Q 被展平成 \[BHN,D\]，每次取 BLOCK_M 个 query。此时 block_shape=\[BLOCK_M,D\]，load(\[r0,0\]) 会读取哪个块？</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：descriptor 给出全局存储视图与每次访问块的形状；load 的 offsets 再指定这一次从视图中的哪个坐标开始。
-• [T#B#base与shape]：base 是已有张量存储的首地址；shape=\[BHN,D\] 声明一个有 BHN 行、D 列的访问视图。创建 descriptor 只是建立访问描述，不会提前读取整个张量。
-• [T#B#strides]：strides 表示某一维索引增加 1 时跨过多少个元素，而不是字节。连续二维视图通常为 \[D,1\]；换算实际字节偏移还要乘元素字节数。
-• [T#B#block_shape]：\[BLOCK_M,D\] 指定每次 load 返回 BLOCK_M 行、D 列的 tile。这是读取结果的局部形状，与整体视图大小不同。
-• [T#B#本次起点]：load(\[r0,0\]) 从第 r0 行、第 0 列开始取该形状的块。若把起点改为 \[r0+BLOCK_M,0\]，就向下移动一个 Q tile；返回形状仍为 \[BLOCK_M,D\]。
-[T#B,!c47f17#边界]：offsets 是每次 load 的参数，不是创建 descriptor 时固定的块起点。以上访问仍须满足该接口的布局、对齐和边界要求；本卡以 Triton 3.7.1 为准。</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">布局由描述给出；大小看 block_shape；位置看 offsets</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · Triton 3.7.1 · 布局由描述给出；大小看 block_shape；位置看 offsets</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 反向统计量、归约与缩放</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 的 Q/K/V descriptor 把多个 batch/head 展平成 \[BHN,D\]，每个 head 占 N 行。若一次 load 跨过当前 head 的末尾，却仍在整个 BHN 行视图之内，descriptor 会自动将越过这个 head 的位置补零吗？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，用 TensorDescriptor 描述展平后的 Q：base 指向连续 Q 的存储，shape=\[BHN,D\]、strides=\[D,1\]（B/H/N/D 分别为 batch 数、head 数、token 数和特征维），block_shape=\[BLOCK_M,D\]。一次 desc.load(\[r0,0\]) 读到的块由哪个参数决定大小、哪个参数决定位置？把起点改成 \[r0+BLOCK_M,0\] 时，读到的块和返回的 shape 各怎样变化？</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会。descriptor 只判断坐标是否越过声明的整体视图，不知道其中哪 N 行属于当前逻辑 head。
-• [T#B#为何仍合法]：跨到下一 head 的行号只要仍小于 BHN，就还是 \[BHN,D\] 中的合法坐标。load 可能正常读到下一 head 的数据，而不会把它当成越界。
-• [T#B#需要保证的范围]：调用方必须正确计算当前 head 的基址，并限制本 program 的 token 扫描范围；batch/head 的逻辑隔离是索引设计的一部分。
-• [T#B#真正越界时]：在默认 zero padding 且访问满足其他约束的情况下，只有超出整个声明视图的元素才会补零。即使尾部有补值，返回 tile 的形状仍由 block_shape 决定。
-[T#B,!c47f17#边界]：自动处理内存视图越界，不等于自动实现 Attention 的 head 边界或 causal 规则；这些逻辑条件仍需由访问范围和 score mask 保证。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：大小由 descriptor 的 block_shape 决定，位置由每次 load 的 offsets 决定。load(\[r0,0\]) 返回从第 r0 行、第 0 列开始的 \[BLOCK_M,D\] 块；起点改成 \[r0+BLOCK_M,0\] 就读下一个 Q tile，返回 shape 仍是 \[BLOCK_M,D\]。
+• [T#B#视图]：base 指向已有存储，shape=\[BHN,D\] 与 strides=\[D,1\] 声明整个访问视图；strides 以元素为单位，换算字节偏移要再乘元素字节数。创建 descriptor 只建立访问描述，不会提前读取整个张量。
+• [T#B#block_shape]：\[BLOCK_M,D\] 是每次 load 返回 tile 的局部形状，属于 descriptor 本身，不随单次 load 改变，也不等于整个视图的大小。
+• [T#B#offsets]：offsets 是每次 load 的参数，不是创建 descriptor 时固定的块起点；改变它只移动读取位置。
+[T#B,!c47f17#边界]：访问仍须满足该接口的布局、对齐和边界要求；offsets 越过视图时按 descriptor 的填充方式处理。</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">视图边界由 descriptor 管；head 范围由索引保证</t>
+          <t xml:space="preserve">布局由描述给出；大小看 block_shape；位置看 offsets</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · Triton 3.7.1 · 视图边界由 descriptor 管；head 范围由索引保证</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · TensorDescriptor、边界与启动准备</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 处理不足一个 tile 的尾部 key 时，假设 descriptor 已把无效位置的 K 和 V 都补成零。能否省掉对这些 key 的 score mask，直接让 softmax 和 pV 计算整个 tile？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，Attention 的 Q/K/V descriptor 把多个 batch/head 展平成 \[BHN,D\] 的视图，每个 head 占连续 N 行。若一次 load 跨过当前 head 的末尾、但仍在整个 BHN 行视图之内，越过 head 末尾的那些行会读到什么？为什么？</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。零 K/V 并没有把无效 key 从 softmax 的归一化集合中删除，它仍可能改变分母。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：会读到下一个 head 的真实数据，不会补零：descriptor 只按声明的整体视图判断越界，不知道其中哪 N 行属于当前 head。
+• [T#B#为何仍合法]：跨到下一 head 的行号只要仍小于 BHN，就是 \[BHN,D\] 中的合法坐标，load 会把它当作正常数据读出。
+• [T#B#需要保证的范围]：调用方必须正确计算当前 head 的基址，并限制本 program 的 token 扫描范围；batch/head 的逻辑隔离是索引设计的一部分。
+• [T#B#真正越界时]：只有超出整个声明视图的元素才会被填充：默认补零，返回 tile 的形状仍由 block_shape 决定。
+• [T#B#填充值（延伸）]：填充值在构造 descriptor 时从 zero（默认）和 nan 两种预设中选定：host 侧 TensorDescriptor 用 padding 参数，kernel 内 tl.make_tensor_descriptor 用 padding_option，nan 只适用于浮点数据。它不能像 tl.load 的 other 那样每次指定任意值；需要别的值时，在 load 后按有效条件替换，或改用带 mask 的普通 tl.load。
+[T#B,!c47f17#边界]：自动处理视图越界，不等于自动实现 Attention 的 head 边界或 causal 规则；这些逻辑条件仍要由访问范围和 score mask 保证。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">视图边界由 descriptor 管；head 范围由索引保证</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-24 · TensorDescriptor、边界与启动准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 处理不足一个 tile 的尾部 key 时，假设 descriptor 已把无效位置的 K 和 V 都补成零。如果省掉对这些 key 的 score mask，直接让 softmax 和 pV 计算整个 tile，结果会怎样？为什么？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：结果会错：零 K/V 没有把无效 key 从 softmax 的归一化集合中删除，每个无效 key 仍向分母贡献一个正项。
 • [T#B#零K的分数]：对有限 query，零 K 的点积为零，乘 scale 后 score 仍为零。但零分数的指数权重不是零。
 [E##S_{ij}=0\quad\Longrightarrow\quad e^{S_{ij}}=1]
 • [T#B#稳定化也不删除]：本卡用自然分数 S 说明，令 m_S=max(S)。减去最大值后，零分数的指数项为 exp(−m_S)，仍会计入分母；稳定化没有删除这个无效 key。若换成 exp2，则最大值也必须使用对应的换底标度。
-• [T#B#零V只影响分子]：零 V 使该项在加权分子中的直接贡献为零，但它仍占据分母，可能把真实 value 的输出权重压小。
-[T#B,!c47f17#边界]：应在 score/概率上按有效 key 条件屏蔽这些位置，使它们对归一化不贡献权重。也不能把 K/V 填成 −∞ 来代替 score mask，因为点积和乘法会产生不同的数值行为。</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+• [T#B#零V只影响分子]：零 V 使该项在加权分子中的直接贡献为零，但它仍占据分母，会把真实 key 的权重都压小。
+[T#B,!c47f17#边界]：应在 score/概率上按有效 key 条件屏蔽这些位置，使它们不参与归一化。也不能改成把 K/V 填成 −∞ 来代替：以 K 为例，−∞ 与 q 的负分量相乘得 +∞、与 0 相乘得 NaN，点积可能变成 +∞ 或 NaN，不能保证得到所需的 −∞。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">零数据不等于零概率；分母也要排除</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 零数据不等于零概率；分母也要排除</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在 Triton 3.7.1 中，普通 tl.load 可用 other 指定 masked 位置的替代值。若改用 TensorDescriptor 的 load，能否同样传入任意 other 值？可选的 padding 在哪里设置？</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：descriptor 不提供任意 other 值；它在构造时选择预设的 zero 或 nan padding，默认是 zero。
-• [T#B#host构造]：host 侧 TensorDescriptor 使用 padding 参数，例如 padding="zero"。这项设置属于 descriptor，而不是每次 load 时单独给出的标量。
-• [T#B#device构造]：kernel 内 tl.make_tensor_descriptor 使用 padding_option 参数，提供同样的预设选择。nan 仅适用于浮点数据。
-• [T#B#其他替代值]：如果运算需要别的值，可以在 load 后根据有效位置条件替换，或者改用普通带 mask 和 other 的 tl.load。选择要满足所用接口的访问约束。
-[T#B,!c47f17#边界]：Attention 的无效 key 需要的是对 score/概率的语义屏蔽；改变 K/V 的越界填充值不能直接代替 softmax mask。本卡的 API 选项限定于 Triton 3.7.1。</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">构造时选预设；不是 load 时传任意 other</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · Triton 3.7.1 · 构造时选预设；不是 load 时传任意 other</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · TensorDescriptor、边界与启动准备</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">把一个 PyTorch 张量传给 Triton 3.7.1 的 NVIDIA TMA descriptor 前，为什么仅检查 is_contiguous() 不够？应怎样检查实际基址与 stride 的基础对齐条件，切片视图又会带来什么问题？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，要把 PyTorch FP16 张量交给 NVIDIA TMA descriptor。设 x 是基址 16 字节对齐的一维连续 FP16 张量，它的切片 x\[1:\] 调用 is_contiguous() 仍返回 True，却不满足 TMA 的布局条件。为什么连续还不够？传入前应检查哪些量？</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：连续性描述元素的排列关系，并不保证视图首地址满足 TMA 对齐；必须检查实际地址和以字节计的步长。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：连续只说明元素按顺序紧挨着，不保证视图首地址对齐：x\[1:\] 的首地址比 x 后移 2 字节，已不是 16 的倍数。传入前要检查视图的实际首地址，以及按字节计的各维 stride。
 • [T#B#需要的量]：设 A=tensor.data_ptr() 为当前视图第一个元素的地址，e 为每元素字节数，s_k 为第 k 维的元素 stride。descriptor 的 strides 参数以元素计，对齐条件则以字节计。
 [E##A\bmod16=0,\qquad s_{last}=1,\qquad (s_ke)\bmod16=0\quad(k&lt;last)]
-• [T#B#切片反例]：一个基址对齐的一维 FP16 张量取 x\[1:\] 后，视图仍可连续，但首地址向后移动 2 字节，从而破坏 16 字节对齐。必须检查传入视图的 data_ptr，而非原始存储的起点。
+• [T#B#偏移规律]：在对齐的存储上偏移 s 个元素、每个元素 e 字节后，视图仍对齐要求 s·e 是 16 的倍数；FP16 每元素 2 字节，偏移须是 8 个元素的倍数。
 • [T#B#contiguous的限制]：如果这个视图本来就连续，contiguous() 可以直接返回它，不会为了对齐自动分配新存储。因此调用 contiguous() 不能替代地址检查。
 [T#B,!c47f17#边界]：这里只列出本路径的基础布局条件。即使这些条件满足，也还需要核对 block_shape、设备支持及后续矩阵乘的限制。</t>
         </is>
@@ -643,138 +643,137 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · Triton 3.7.1 · 查实际首地址与字节步长；连续不保证对齐</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · TensorDescriptor、边界与启动准备</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">所学 Attention 的普通 FP16 路径中，D 表示每个 head 的特征维度。wrapper 在 host 侧先用 dummy_block 创建 TensorDescriptor，而 autotune 会尝试不同 BLOCK_M/BLOCK_N。为什么每次配置运行前必须由 pre-hook 更新 block_shape，不能指望 kernel 中的 _maybe_make_tensor_desc 自动改正确？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，把 Attention 的 K/V 读取从“指针加 mask 的 tl.load”改成 TensorDescriptor 的 desc.load。在支持 TMA 的 NVIDIA GPU 上，这种写法带来了什么能力？又有哪些事情不能据此断言？</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它让规则矩形块的访问可以交给 TMA 硬件处理多维搬运、寻址和越界填充，为访存与计算重叠创造条件；但这只是能力，不保证比普通 tl.load 更快。
+• [T#B#带来的能力]：descriptor 事先声明视图的 shape、strides 和 block_shape，之后每次 load 只给块起点；在支持的硬件上，块的地址计算和越界填充由 TMA 完成。
+• [T#B#不保证更快]：实际收益取决于 descriptor 的构造成本、块配置、编译结果和设备，要实测才能下结论。
+• [T#B#不说明存放位置]：desc.load 返回的是参与计算的 tl.tensor，不能只凭这一行判断数据始终放在某种片上存储里。
+[T#B,!c47f17#边界]：这些能力以硬件支持 TMA 为前提，张量还要满足 descriptor 的对齐与布局条件。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TMA 提供搬运与填充的能力，不提供更快的保证</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-24 · TensorDescriptor、边界与启动准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 官方 fused-attention 教程（快照版）的普通 FP16 路径中，D 表示每个 head 的特征维度。wrapper 在 host 侧先用 dummy_block 创建 TensorDescriptor，而 autotune 会尝试不同 BLOCK_M/BLOCK_N。为什么每次配置运行前必须由 pre-hook 更新 block_shape，不能指望 kernel 中的 _maybe_make_tensor_desc 自动改正确？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：host 传入的已经是 descriptor，helper 会原样返回它；因此进入 kernel 前，它的块大小就必须与当前配置一致。
 • [T#B#占位阶段]：dummy_block 只是构造 descriptor 时的占位形状。实际一轮候选可能选择不同的 Q tile 行数 BLOCK_M 和 K/V tile 行数 BLOCK_N。
 • [T#B#pre-hook的职责]：运行每个候选前，把 Q/O descriptor 的 block_shape 改为 \[BLOCK_M,D\]，K/V 改为 \[BLOCK_N,D\]，使 load/store 的实际形状匹配该候选。
 • [T#B#helper两条路径]：收到普通指针时，helper 才使用 shape、strides、block_shape 构造 descriptor；收到已有 descriptor 时直接返回，额外传入的 block_shape 不会覆盖对象。
-[T#B,!c47f17#边界]：pre-hook、grid 和 kernel 内计算形状必须使用同一候选配置。这个问题来自所学教程的 host descriptor 调用方式，不能假设所有 descriptor 都必须采用 dummy_block。</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+[T#B,!c47f17#边界]：pre-hook、grid 和 kernel 内计算形状必须使用同一候选配置。这个问题来自该教程的 host descriptor 调用方式，不能假设所有 descriptor 都必须采用 dummy_block。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t xml:space="preserve">当前配置 → 更新 descriptor → 原样传入 kernel</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 所学源码快照 · 当前配置 → 更新 descriptor → 原样传入 kernel</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比较 FP8 E5M2 和 FP16 的表示精度：前者为 1 位符号、5 位指数、2 位显式小数，后者为 1、5、10。固定同一个正规数指数区间，E5M2 相邻可表示数的间距是 FP16 的多少倍？为什么指数位数相同仍不代表精度相同？</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：E5M2 的相邻间距是 FP16 的 256 倍；相同指数位数没有补回少掉的小数位。
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-24 · TensorDescriptor、边界与启动准备；FP8、布局与执行配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">把 FP16 数值转换为 FP8 E5M2 时，即使数值落在 E5M2 的范围内、没有溢出，误差为什么仍可能明显变大？已知 E5M2 为 1 位符号、5 位指数、2 位显式小数，FP16 为 1、5、10。请用同一正规数指数区间内相邻可表示数的间距说明。</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为小数位少：两者都有 5 位指数，但 E5M2 只有 2 位显式小数。同一正规指数区间内，它的相邻间距是 FP16 的 2^(10−2)=256 倍，转换时只能舍入到更稀疏的点上。
 • [T#B#正规数模型]：在固定指数 e 的正规区间中，数值可写成符号×2^e×(1+f/2^p)，p 是显式小数位数。f 每增加 1，相邻数就相差 2^(e−p)。
 [E##\frac{2^{e-2}}{2^{e-10}}=2^8=256]
 • [T#B#含义]：E5M2 只有 2 位显式小数，同一个区间内可表示的点更稀疏。把 FP16 数值转为它时，即使不发生范围溢出，也可能产生更大的舍入误差。
 [T#B,!c47f17#边界]：这里比较的是同一正规指数区间的间距，不覆盖零、非正规数或特殊值。指数位数主要关联范围，小数位数影响局部表示分辨率。</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">范围看指数；精度看小数位</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 范围看指数；精度看小数位</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">所学 FP8 Attention 为 V 调整布局：B/H 分别是 batch/head 数，N 是 token 数，D 是特征维。从连续的 \[B,H,N,D\] 张量出发，先 permute 成 \[B,H,D,N\] 并 contiguous()，再用逆 permute 恢复 \[B,H,N,D\]。最终 shape 已恢复，为什么存储布局仍然改变？删掉中间 contiguous() 又会怎样？</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attention 学习记录 09-24 · FP8、布局与执行配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 官方 fused-attention 教程（快照版）的 FP8 路径为 V 调整布局：B/H 分别是 batch/head 数，N 是 token 数，D 是特征维。从连续的 \[B,H,N,D\] 张量出发，先 permute 成 \[B,H,D,N\] 并 contiguous()，再用逆 permute 恢复 \[B,H,N,D\]。最终 shape 已恢复，为什么存储布局仍然改变？删掉中间 contiguous() 又会怎样？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：中间 contiguous() 按转置后的轴顺序复制了数据；逆 permute 只恢复逻辑轴顺序，不会把这次复制后的存储重新排列回去。
 • [T#B#原布局]：连续 \[B,H,N,D\] 的末两维 stride 是 \[D,1\]，同一个 token 的 D 个特征相邻。令 g=bH+h，则元素 (g,n,d) 的线性偏移为 gND+nD+d。
 • [T#B#复制后]：在 \[B,H,D,N\] 下做 contiguous 后，同一个特征的 N 个 token 相邻。再恢复逻辑 shape，末两维 stride 变成 \[1,N\]，元素偏移为 gND+dN+n。
 [E##gND+nD+d\ \longrightarrow\ gND+dN+n]
 • [T#B#删除中间复制]：仅连续做两次互逆 permute 会把 shape 和 stride 都恢复，底层存储没有搬动。对于原本连续的张量，最后再调用 contiguous 通常也无需复制。
-[T#B,!c47f17#边界]：判断布局必须同时看 shape、stride 和是否发生实际复制。此处解释的是所学 V 重排；后续转换为 FP8 的 dtype 操作，与轴布局变化是另一件事。</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+[T#B,!c47f17#边界]：判断布局必须同时看 shape、stride 和是否发生实际复制。此处解释的是该教程的 V 重排；后续转换为 FP8 的 dtype 操作，与轴布局变化是另一件事。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t xml:space="preserve">shape 相同不保证存储布局相同</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 所学源码快照 · shape 相同不保证存储布局相同</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">验证两个 Attention 实现的反向结果时，参考实现先调用 backward(dout)，然后再运行被测实现。除了 Q/K/V 相同，还必须固定哪些输入条件？为什么保存参考梯度后要清空叶子张量的 .grad？</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：两边必须对同一计算问题、同一上游梯度求导，并避免后一次 backward 把结果累加到已有梯度上。
-• [T#B#同一前向问题]：Q/K/V、causal 开关与原始 scale 都要相同，否则前向函数本身就不同。
-• [T#B#同一dout]：dout 即 dO，决定损失对输出各元素的加权。可把 backward(dout) 理解为对固定 dout 的标量 L=Σ(O*dout) 求导；换一个 dout，得到的梯度通常也会变。
-• [T#B#保存再清空]：先保存参考的 dQ/dK/dV，再清空对应叶子张量的 .grad。PyTorch 的 backward 会累计叶子梯度，否则第二次读到的可能是两次结果之和。
-[T#B,!c47f17#边界]：输入条件或梯度累计状态不同，得到的差异不能直接归因于被测 kernel 错误。比较前向 O 一致，也不能替代对上游 dO 的一致性检查。</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">同 QKV、同规则、同 dO；清空累计梯度</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 所学源码快照 · 同 QKV、同规则、同 dO；清空累计梯度</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · FP8、布局与执行配置</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">所学 Attention benchmark 用前向 FLOP 数乘 2.5 来估算反向工作量。这里 FLOP 指浮点运算次数，B/H/N/D 分别是 batch、head、token 和特征维。2.5 的来源是什么，它能否预测反向耗时也是前向的 2.5 倍？</t>
+          <t xml:space="preserve">对照两个 Attention 实现的反向结果：参考实现先执行 backward(dout)，再让被测实现执行反向，两边的 Q/K/V、causal 开关和 scale 都相同。为什么两边还必须使用同一个上游梯度 dout？</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：2.5 是主要矩阵乘工作量的报告模型：反向按五次、前向按两次估算，因此得到 5/2；它不是耗时预测。
-• [T#B#前向口径]：QKᵀ 与 PV 各有约 BHN²D 次乘加，按一次乘加计两个 FLOP，合计约 4BHN²D。
-• [T#B#反向口径]：benchmark 用五次主要矩阵乘来代表反向，相对前向两次形成 2.5 系数。它是一种统一报告口径，不是逐条核算该 kernel 执行的所有指令。
-• [T#B#实际实现]：不同梯度路径还可能重复重算概率相关项，并包含归约、指数、读写等工作。causal 把工作量乘 0.5 也只是近似。
-[T#B,!c47f17#边界]：耗时同时受数据搬运、并行度、资源与执行组织影响，必须实际测量。不能由这个系数断言反向必定慢 2.5 倍，也不能把报告 FLOP 当作精确的硬件指令数。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 dout 也是反向的输入：backward(dout) 可理解为对固定 dout 的标量 L=Σ(O*dout) 求导，换一个 dout 就是在求另一个损失的梯度，两边的差异不能归因于 kernel。
+• [T#B#同一前向问题]：Q/K/V、causal 开关与原始 scale 决定前向函数本身；它们相同只保证两边算的是同一个 O。
+• [T#B#dout的作用]：dout 即 dO，决定损失对输出各元素的加权；换一个 dout，得到的 dQ/dK/dV 通常也会变。
+[T#B,!c47f17#边界]：另需注意 PyTorch 的 backward 会累计叶子张量的 .grad：保存参考梯度后要清空，否则第二次读到的是两次结果之和。前向 O 一致也不能替代对 dout 一致性的检查。</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLOP 模型 ≠ 实际指令数 ≠ 耗时</t>
+          <t xml:space="preserve">dout 也是反向输入；同一个 dout 才能比较梯度</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 所学源码快照 · FLOP 模型 ≠ 实际指令数 ≠ 耗时</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 正确性与 benchmark 边界</t>
         </is>
       </c>
     </row>
@@ -786,11 +785,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：相同 Q 保证对同一个 key 的分数相同；还需要每行使用同一组有效 key，才能推出相同的权重、O 和 M。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：相同 Q 让每行对同一个 key 的分数相同；只有每行的有效 key 集合也相同，权重、O 和 M 才相同。causal 下有效集合随 query 位置变化，这个前提不再成立。
 • [T#B#非causal]：每个 query 都访问完整 K/V，因此分数序列和归一化集合都相同。softmax 概率相同，加权相同的 V 后输出也相同，分母的 log₂ 即 M 同样相同。
-• [T#B#causal]：第 i 行只访问 j≤i 的前缀，包含自身。即使对共同 key 的分数一样，参与归一化的集合仍随 query 位置改变，所以不能继续推断所有 O/M 行相同。
-• [T#B#输出并非必然两两不同]：有效集合变化通常会使 O 变化，但特殊的 V 仍可能使某些行输出相同；例如所有 value 相同，归一化后的加权和仍可能相同。
-[T#B,!c47f17#边界]：这里讨论同一 head、同一 scale 和一致输入下的数学关系。浮点实现会有舍入误差；不能把“通常变化”加强成“任意两行必定不同”。</t>
+• [T#B#causal下的M]：第 i 行只访问 j≤i 的前缀，包含自身。分数有限时，每多一个有效 key，分母就多一个正项，所以 M 随有效前缀严格增长，各行的 M 互不相同。
+• [T#B#causal下的O]：O 通常随之变化，但不必两两不同：例如所有 value 向量都相同时，每行输出都等于这个 value，各行必然相同。
+[T#B,!c47f17#边界]：这里讨论同一 head、同一 scale、有限 score 下的数学关系；浮点实现还有舍入误差。“O 通常变化”不能加强成“任意两行的 O 必定不同”。</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -800,7 +799,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention 学习记录 09-24 · 相同 score + 相同有效集合</t>
+          <t xml:space="preserve">Attention 学习记录 09-24 · 实践修改与 A4 独立解释</t>
         </is>
       </c>
     </row>
